--- a/docs/specs/오염물질 배출관리_데이터 정의서_v0.1.xlsx
+++ b/docs/specs/오염물질 배출관리_데이터 정의서_v0.1.xlsx
@@ -7844,7 +7844,7 @@
       </c>
       <c r="H5" s="46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I5" s="40" t="n"/>
@@ -17187,7 +17187,7 @@
       </c>
       <c r="H46" s="24" t="inlineStr">
         <is>
-          <t>[설계] 실측+예측 한 축</t>
+          <t>[설계] 관측 구간 6시간의 시각 · 수집 주기 5분이라 72점 [원문 p.55]</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
@@ -17197,7 +17197,7 @@
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>차트 x축 · 툴팁</t>
         </is>
       </c>
       <c r="K46" s="8" t="inlineStr"/>
@@ -17220,7 +17220,7 @@
       </c>
       <c r="D47" s="24" t="inlineStr">
         <is>
-          <t>실측값</t>
+          <t>계열 값</t>
         </is>
       </c>
       <c r="E47" s="24" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="H47" s="24" t="inlineStr">
         <is>
-          <t>[설계] 실측 구간에만, 예측 구간은 null(E4)</t>
+          <t>[설계] 그 시각의 값. null은 결측이며 0으로 채우지 않는다(E4)</t>
         </is>
       </c>
       <c r="I47" s="8" t="inlineStr">
@@ -17250,7 +17250,7 @@
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>계열 선</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr"/>
@@ -17273,17 +17273,17 @@
       </c>
       <c r="D48" s="24" t="inlineStr">
         <is>
-          <t>예측값</t>
+          <t>값의 출처</t>
         </is>
       </c>
       <c r="E48" s="24" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>measured|softSensed</t>
         </is>
       </c>
       <c r="F48" s="24" t="inlineStr">
         <is>
-          <t>mg/L</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G48" s="24" t="inlineStr">
@@ -17293,7 +17293,7 @@
       </c>
       <c r="H48" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.32·65]</t>
+          <t>TOC·유량은 직접 계측 [원문 p.55] · TN·TP는 소프트 센싱 [원문 발표 p.17] [회의 2026-08-20] · 한 화면에서 둘이 섞이면 추정이 계측으로 읽힌다(E3)</t>
         </is>
       </c>
       <c r="I48" s="8" t="inlineStr">
@@ -17303,7 +17303,7 @@
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>계열 색 · 범례 · 근거 줄</t>
         </is>
       </c>
       <c r="K48" s="8" t="inlineStr"/>
@@ -17311,7 +17311,7 @@
     <row r="49" s="35">
       <c r="A49" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-009</t>
+          <t>REQ-AD-010</t>
         </is>
       </c>
       <c r="B49" s="24" t="inlineStr">
@@ -17326,7 +17326,7 @@
       </c>
       <c r="D49" s="24" t="inlineStr">
         <is>
-          <t>신뢰구간 하한</t>
+          <t>최근 6시간 최대</t>
         </is>
       </c>
       <c r="E49" s="24" t="inlineStr">
@@ -17336,17 +17336,17 @@
       </c>
       <c r="F49" s="24" t="inlineStr">
         <is>
-          <t>mg/L</t>
+          <t>항목 단위</t>
         </is>
       </c>
       <c r="G49" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[파생: 관측 구간 최대]</t>
         </is>
       </c>
       <c r="H49" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.32·65] · 신뢰수준 [TBD]</t>
+          <t>[원문 발표 p.16 그림]이 차트 아래에 최대 예측값 62.4 NTU를 함께 낸다 · 예측이 아니라 관측 구간의 최대다 [INC-109] — 예측 구간을 내렸으므로 이름도 바뀌었다 · 값이 없으면 null(E4)</t>
         </is>
       </c>
       <c r="I49" s="8" t="inlineStr">
@@ -17356,19 +17356,19 @@
       </c>
       <c r="J49" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>산출 근거</t>
         </is>
       </c>
       <c r="K49" s="8" t="inlineStr">
         <is>
-          <t>TBD 원문 미확정</t>
+          <t>INC-109 원문 모순 — 채택안은 출처 열에 적었다</t>
         </is>
       </c>
     </row>
     <row r="50" s="35">
       <c r="A50" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-009</t>
+          <t>REQ-AD-010</t>
         </is>
       </c>
       <c r="B50" s="24" t="inlineStr">
@@ -17383,27 +17383,27 @@
       </c>
       <c r="D50" s="24" t="inlineStr">
         <is>
-          <t>신뢰구간 상한</t>
+          <t>유량 예측 계열</t>
         </is>
       </c>
       <c r="E50" s="24" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>ForecastPoint[]</t>
         </is>
       </c>
       <c r="F50" s="24" t="inlineStr">
         <is>
-          <t>mg/L</t>
+          <t>m³/day</t>
         </is>
       </c>
       <c r="G50" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>오염도와 같은 생성 규약</t>
         </is>
       </c>
       <c r="H50" s="24" t="inlineStr">
         <is>
-          <t>동일</t>
+          <t>[원문 발표 p.11 그림] "1~6시간 후 유량 변화 예측" [INC-95 판정] · R²는 표시하지 않는다 — 성능 목표가 수질 예측뿐이다 [원문 발표 p.26]</t>
         </is>
       </c>
       <c r="I50" s="8" t="inlineStr">
@@ -17416,12 +17416,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K50" s="8" t="inlineStr"/>
+      <c r="K50" s="8" t="inlineStr">
+        <is>
+          <t>INC-95 원문 모순 — 채택안은 출처 열에 적었다</t>
+        </is>
+      </c>
     </row>
     <row r="51" s="35">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-010</t>
+          <t>REQ-AD-014</t>
         </is>
       </c>
       <c r="B51" s="24" t="inlineStr">
@@ -17436,32 +17440,32 @@
       </c>
       <c r="D51" s="24" t="inlineStr">
         <is>
-          <t>최대 예측값</t>
+          <t>대상 항목 코드</t>
         </is>
       </c>
       <c r="E51" s="24" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>TOC|TN|TP|flow</t>
         </is>
       </c>
       <c r="F51" s="24" t="inlineStr">
         <is>
-          <t>항목 단위</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G51" s="24" t="inlineStr">
         <is>
-          <t>[파생: 예측 구간 최대] — 실측은 세지 않는다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H51" s="24" t="inlineStr">
         <is>
-          <t>[원문 발표 p.16 그림] 예측 화면이 차트 아래에 최대 예측값 62.4 NTU를 함께 낸다 · 예측이 없으면 null(E4)</t>
+          <t>[원문 p.68] + 유량 [INC-95 판정] · 요약이 코드를 함께 낸다 — 소비처가 표시명을 잘라 코드를 되찾지 않게(기준값 조회·3단 차트가 쓴다)</t>
         </is>
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J51" s="8" t="inlineStr">
@@ -17469,12 +17473,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K51" s="8" t="inlineStr"/>
+      <c r="K51" s="8" t="inlineStr">
+        <is>
+          <t>INC-95 원문 모순 — 채택안은 출처 열에 적었다</t>
+        </is>
+      </c>
     </row>
     <row r="52" s="35">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-010</t>
+          <t>REQ-AD-014</t>
         </is>
       </c>
       <c r="B52" s="24" t="inlineStr">
@@ -17489,27 +17497,27 @@
       </c>
       <c r="D52" s="24" t="inlineStr">
         <is>
-          <t>유량 예측 계열</t>
+          <t>대상 항목명</t>
         </is>
       </c>
       <c r="E52" s="24" t="inlineStr">
         <is>
-          <t>ForecastPoint[]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F52" s="24" t="inlineStr">
         <is>
-          <t>m³/day</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G52" s="24" t="inlineStr">
         <is>
-          <t>오염도와 같은 생성 규약</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H52" s="24" t="inlineStr">
         <is>
-          <t>[원문 발표 p.11 그림] "1~6시간 후 유량 변화 예측" [INC-95 판정] · R²는 표시하지 않는다 — 성능 목표가 수질 예측뿐이다 [원문 발표 p.26]</t>
+          <t>[원문 p.68] TOC/TN/TP</t>
         </is>
       </c>
       <c r="I52" s="8" t="inlineStr">
@@ -17522,11 +17530,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K52" s="8" t="inlineStr">
-        <is>
-          <t>INC-95 원문 모순 — 채택안은 출처 열에 적었다</t>
-        </is>
-      </c>
+      <c r="K52" s="8" t="inlineStr"/>
     </row>
     <row r="53" s="35">
       <c r="A53" s="24" t="inlineStr">
@@ -17546,17 +17550,17 @@
       </c>
       <c r="D53" s="24" t="inlineStr">
         <is>
-          <t>대상 항목 코드</t>
+          <t>단위</t>
         </is>
       </c>
       <c r="E53" s="24" t="inlineStr">
         <is>
-          <t>TOC|TN|TP|flow</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F53" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="G53" s="24" t="inlineStr">
@@ -17566,12 +17570,12 @@
       </c>
       <c r="H53" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.68] + 유량 [INC-95 판정] · 요약이 코드를 함께 낸다 — 소비처가 표시명을 잘라 코드를 되찾지 않게(기준값 조회·3단 차트가 쓴다)</t>
+          <t>[원문 p.68]</t>
         </is>
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J53" s="8" t="inlineStr">
@@ -17579,11 +17583,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K53" s="8" t="inlineStr">
-        <is>
-          <t>INC-95 원문 모순 — 채택안은 출처 열에 적었다</t>
-        </is>
-      </c>
+      <c r="K53" s="8" t="inlineStr"/>
     </row>
     <row r="54" s="35">
       <c r="A54" s="24" t="inlineStr">
@@ -17603,7 +17603,7 @@
       </c>
       <c r="D54" s="24" t="inlineStr">
         <is>
-          <t>대상 항목명</t>
+          <t>대상 항목 코드·명</t>
         </is>
       </c>
       <c r="E54" s="24" t="inlineStr">
@@ -17623,7 +17623,7 @@
       </c>
       <c r="H54" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.68] TOC/TN/TP</t>
+          <t>[원문 p.68] TOC/TN/TP · 경향 카드 3개의 식별</t>
         </is>
       </c>
       <c r="I54" s="8" t="inlineStr">
@@ -17656,17 +17656,17 @@
       </c>
       <c r="D55" s="24" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>표시 자릿수</t>
         </is>
       </c>
       <c r="E55" s="24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="F55" s="24" t="inlineStr">
         <is>
-          <t>mg/L</t>
+          <t>자리</t>
         </is>
       </c>
       <c r="G55" s="24" t="inlineStr">
@@ -17676,12 +17676,12 @@
       </c>
       <c r="H55" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.68]</t>
+          <t>[PROVISIONAL] TOC·TN 1 · TP 2. 요약과 경향 카드가 각각 값과 함께 낸다 — 위젯이 임의로 반올림하거나 프로파일을 되찾아 오지 못하게(E1)</t>
         </is>
       </c>
       <c r="I55" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J55" s="8" t="inlineStr">
@@ -17689,12 +17689,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K55" s="8" t="inlineStr"/>
+      <c r="K55" s="8" t="inlineStr">
+        <is>
+          <t>임시값 — 확정 시 src/shared/config/provisional.ts 한 파일을 교체한다</t>
+        </is>
+      </c>
     </row>
     <row r="56" s="35">
       <c r="A56" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-014</t>
+          <t>REQ-AD-010</t>
         </is>
       </c>
       <c r="B56" s="24" t="inlineStr">
@@ -17709,12 +17713,12 @@
       </c>
       <c r="D56" s="24" t="inlineStr">
         <is>
-          <t>대상 항목 코드·명</t>
+          <t>통신 상태</t>
         </is>
       </c>
       <c r="E56" s="24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F56" s="24" t="inlineStr">
@@ -17729,17 +17733,17 @@
       </c>
       <c r="H56" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.68] TOC/TN/TP · 경향 카드 3개의 식별</t>
+          <t>[설계] 두절이면 추정도 산출되지 않는다 — 값이 전부 null이다</t>
         </is>
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J56" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>빈 상태 문구</t>
         </is>
       </c>
       <c r="K56" s="8" t="inlineStr"/>
@@ -17747,7 +17751,7 @@
     <row r="57" s="35">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-014</t>
+          <t>REQ-AD-005</t>
         </is>
       </c>
       <c r="B57" s="24" t="inlineStr">
@@ -17762,17 +17766,17 @@
       </c>
       <c r="D57" s="24" t="inlineStr">
         <is>
-          <t>표시 자릿수</t>
+          <t>산출 시각</t>
         </is>
       </c>
       <c r="E57" s="24" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>ISO8601</t>
         </is>
       </c>
       <c r="F57" s="24" t="inlineStr">
         <is>
-          <t>자리</t>
+          <t>KST</t>
         </is>
       </c>
       <c r="G57" s="24" t="inlineStr">
@@ -17782,12 +17786,12 @@
       </c>
       <c r="H57" s="24" t="inlineStr">
         <is>
-          <t>[PROVISIONAL] TOC·TN 1 · TP 2. 요약과 경향 카드가 각각 값과 함께 낸다 — 위젯이 임의로 반올림하거나 프로파일을 되찾아 오지 못하게(E1)</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J57" s="8" t="inlineStr">
@@ -17795,16 +17799,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K57" s="8" t="inlineStr">
-        <is>
-          <t>임시값 — 확정 시 src/shared/config/provisional.ts 한 파일을 교체한다</t>
-        </is>
-      </c>
+      <c r="K57" s="8" t="inlineStr"/>
     </row>
     <row r="58" s="35">
       <c r="A58" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-009</t>
+          <t>REQ-AD-005</t>
         </is>
       </c>
       <c r="B58" s="24" t="inlineStr">
@@ -17819,17 +17819,17 @@
       </c>
       <c r="D58" s="24" t="inlineStr">
         <is>
-          <t>예측 지평</t>
+          <t>입력 대상 기간</t>
         </is>
       </c>
       <c r="E58" s="24" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F58" s="24" t="inlineStr">
         <is>
-          <t>시간</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G58" s="24" t="inlineStr">
@@ -17839,7 +17839,7 @@
       </c>
       <c r="H58" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.32·65] 1~6시간</t>
+          <t>[원문 p.65] 과거 24시간 다변량 시계열 E3</t>
         </is>
       </c>
       <c r="I58" s="8" t="inlineStr">
@@ -17857,7 +17857,7 @@
     <row r="59" s="35">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-010</t>
+          <t>REQ-AD-005</t>
         </is>
       </c>
       <c r="B59" s="24" t="inlineStr">
@@ -17872,12 +17872,12 @@
       </c>
       <c r="D59" s="24" t="inlineStr">
         <is>
-          <t>통신 상태</t>
+          <t>산출 모델</t>
         </is>
       </c>
       <c r="E59" s="24" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F59" s="24" t="inlineStr">
@@ -17892,12 +17892,12 @@
       </c>
       <c r="H59" s="24" t="inlineStr">
         <is>
-          <t>[설계] 두절이면 예측도 산출되지 않는다</t>
+          <t>[원문 p.65·66] E3</t>
         </is>
       </c>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J59" s="8" t="inlineStr">
@@ -17910,7 +17910,7 @@
     <row r="60" s="35">
       <c r="A60" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-005</t>
+          <t>REQ-AD-011</t>
         </is>
       </c>
       <c r="B60" s="24" t="inlineStr">
@@ -17925,27 +17925,27 @@
       </c>
       <c r="D60" s="24" t="inlineStr">
         <is>
-          <t>산출 시각</t>
+          <t>경향</t>
         </is>
       </c>
       <c r="E60" s="24" t="inlineStr">
         <is>
-          <t>ISO8601</t>
+          <t>rising|steady|falling | null</t>
         </is>
       </c>
       <c r="F60" s="24" t="inlineStr">
         <is>
-          <t>KST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G60" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[파생: 계열 앞뒤 절반의 평균 차이 &gt; 항목 진폭 × 0.5]</t>
         </is>
       </c>
       <c r="H60" s="24" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>[원문 발표 p.17] 상승/유지/하락 [INC-05] · null은 판정하지 않았다는 뜻이다 — 표본이 4점 미만이면 방향을 낼 수 없다. 예전에는 시나리오 세기로 정해 차트가 내려가는데 카드가 상승이라 말할 수 있었다(E4)</t>
         </is>
       </c>
       <c r="I60" s="8" t="inlineStr">
@@ -17955,15 +17955,19 @@
       </c>
       <c r="J60" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K60" s="8" t="inlineStr"/>
+          <t>경향 칩 — null이면 칩이 없다</t>
+        </is>
+      </c>
+      <c r="K60" s="8" t="inlineStr">
+        <is>
+          <t>INC-05 원문 모순 — 채택안은 출처 열에 적었다</t>
+        </is>
+      </c>
     </row>
     <row r="61" s="35">
       <c r="A61" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-005</t>
+          <t>REQ-AD-011</t>
         </is>
       </c>
       <c r="B61" s="24" t="inlineStr">
@@ -17978,37 +17982,37 @@
       </c>
       <c r="D61" s="24" t="inlineStr">
         <is>
-          <t>입력 대상 기간</t>
+          <t>경향 값</t>
         </is>
       </c>
       <c r="E61" s="24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number | null</t>
         </is>
       </c>
       <c r="F61" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="G61" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[파생: 계열 마지막 값]</t>
         </is>
       </c>
       <c r="H61" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.65] 과거 24시간 다변량 시계열 E3</t>
+          <t>[설계] 차트와 카드를 일치시키려고 · 통신 두절이면 null(산출 중단, 0으로 채우지 않는다 E4)</t>
         </is>
       </c>
       <c r="I61" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J61" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>화면에 숫자로 내지 않는다 [회의 2026-08-20] — 소프트 센싱은 절대값 정확도를 맞추기 어려워 기준 대비만 낸다. 기준 판정의 입력으로만 쓴다</t>
         </is>
       </c>
       <c r="K61" s="8" t="inlineStr"/>
@@ -18016,7 +18020,7 @@
     <row r="62" s="35">
       <c r="A62" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-005</t>
+          <t>REQ-AD-025</t>
         </is>
       </c>
       <c r="B62" s="24" t="inlineStr">
@@ -18031,7 +18035,7 @@
       </c>
       <c r="D62" s="24" t="inlineStr">
         <is>
-          <t>산출 모델</t>
+          <t>판정 문구</t>
         </is>
       </c>
       <c r="E62" s="24" t="inlineStr">
@@ -18046,12 +18050,12 @@
       </c>
       <c r="G62" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[파생: 값 없음 &gt; 기준 판정 &gt; 기준 미설정]</t>
         </is>
       </c>
       <c r="H62" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.65·66] E3</t>
+          <t>[설계] 축은 기준치 하나다 [사용자 지적 2026-08-21] — 시간·분포 대비를 판정 자리에 놓으면 화면이 묻지 않은 것을 답한다. 값 없음을 가장 먼저 본다 — isOverLimit이 "값이 없다"와 "기준이 없다"를 같은 null로 내므로 순서가 뒤집히면 통신 두절 사업장이 기준 판정을 주장한다 · 세 화면(오염도 추정·통합 관제·리포트)이 같은 함수를 쓴다</t>
         </is>
       </c>
       <c r="I62" s="8" t="inlineStr">
@@ -18061,7 +18065,7 @@
       </c>
       <c r="J62" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>경향 카드 헤드라인 · 리포트 판정 열</t>
         </is>
       </c>
       <c r="K62" s="8" t="inlineStr"/>
@@ -18069,7 +18073,7 @@
     <row r="63" s="35">
       <c r="A63" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-011</t>
+          <t>REQ-AD-025</t>
         </is>
       </c>
       <c r="B63" s="24" t="inlineStr">
@@ -18084,12 +18088,12 @@
       </c>
       <c r="D63" s="24" t="inlineStr">
         <is>
-          <t>경향</t>
+          <t>판정 근거</t>
         </is>
       </c>
       <c r="E63" s="24" t="inlineStr">
         <is>
-          <t>rising|steady|falling</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F63" s="24" t="inlineStr">
@@ -18104,7 +18108,7 @@
       </c>
       <c r="H63" s="24" t="inlineStr">
         <is>
-          <t>[원문 발표 p.17] 상승/유지/하락 [INC-05]</t>
+          <t>E3 기준 판정이면 출처, 미설정이면 무엇을 설정해야 하는지 — 사업장 분류 / 시트 / 항목값 셋을 구분한다(할 일이 다르다)</t>
         </is>
       </c>
       <c r="I63" s="8" t="inlineStr">
@@ -18114,19 +18118,15 @@
       </c>
       <c r="J63" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K63" s="8" t="inlineStr">
-        <is>
-          <t>INC-05 원문 모순 — 채택안은 출처 열에 적었다</t>
-        </is>
-      </c>
+          <t>경향 카드 근거 줄</t>
+        </is>
+      </c>
+      <c r="K63" s="8" t="inlineStr"/>
     </row>
     <row r="64" s="35">
       <c r="A64" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-011</t>
+          <t>REQ-AD-025</t>
         </is>
       </c>
       <c r="B64" s="24" t="inlineStr">
@@ -18141,27 +18141,27 @@
       </c>
       <c r="D64" s="24" t="inlineStr">
         <is>
-          <t>경향 값</t>
+          <t>적용 기준치 표기</t>
         </is>
       </c>
       <c r="E64" s="24" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>string | null</t>
         </is>
       </c>
       <c r="F64" s="24" t="inlineStr">
         <is>
-          <t>mg/L</t>
+          <t>항목 단위</t>
         </is>
       </c>
       <c r="G64" s="24" t="inlineStr">
         <is>
-          <t>[파생: 예측 계열 마지막 지점]</t>
+          <t>[파생: 상한만 있으면 ≤ 40.0, 양방향이면 5.80–8.60]</t>
         </is>
       </c>
       <c r="H64" s="24" t="inlineStr">
         <is>
-          <t>[설계] 차트와 카드를 일치시키려고 · 통신 두절이면 null(산출 중단, 0으로 채우지 않는다 E4)</t>
+          <t>[회의 2026-08-20: 어느 지역의 TN 기준치는 몇이고 TP 기준치는 몇인 이러한 사항의 모니터링도 필요] — 판정만 있으면 무엇에 견준 것인지 알 수 없다</t>
         </is>
       </c>
       <c r="I64" s="8" t="inlineStr">
@@ -18171,7 +18171,7 @@
       </c>
       <c r="J64" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>적용 기준치 패널 · 카드 기준 ≤ …</t>
         </is>
       </c>
       <c r="K64" s="8" t="inlineStr"/>
@@ -18179,7 +18179,7 @@
     <row r="65" s="35">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-011</t>
+          <t>REQ-AD-025</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
@@ -18194,27 +18194,27 @@
       </c>
       <c r="D65" s="24" t="inlineStr">
         <is>
-          <t>결정계수 R²</t>
+          <t>사업장 분류 표기</t>
         </is>
       </c>
       <c r="E65" s="24" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>string | null</t>
         </is>
       </c>
       <c r="F65" s="24" t="inlineStr">
         <is>
-          <t>0~1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G65" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[파생: 지역구분 · 배출량 규모]</t>
         </is>
       </c>
       <c r="H65" s="24" t="inlineStr">
         <is>
-          <t>TN·TP만 [원문 p.27] · TOC는 원문에 없어 null [INC-20·21]</t>
+          <t>[공정자료 p.11] 기준표가 그 두 축으로 갈린다 · 한쪽만 골랐으면 나머지를 규모 미설정으로 남긴다 — 빈 칸으로 두면 다 골랐다고 읽힌다</t>
         </is>
       </c>
       <c r="I65" s="8" t="inlineStr">
@@ -18224,39 +18224,35 @@
       </c>
       <c r="J65" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K65" s="8" t="inlineStr">
-        <is>
-          <t>INC-20 원문 모순 — 채택안은 출처 열에 적었다</t>
-        </is>
-      </c>
+          <t>패널 머리말 · 카드</t>
+        </is>
+      </c>
+      <c r="K65" s="8" t="inlineStr"/>
     </row>
     <row r="66" s="35">
       <c r="A66" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-031</t>
+          <t>REQ-AD-025</t>
         </is>
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>SCR-OP-009</t>
+          <t>SCR-OP-004</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
         <is>
-          <t>수분석 검증</t>
+          <t>예측</t>
         </is>
       </c>
       <c r="D66" s="24" t="inlineStr">
         <is>
-          <t>검증 원천</t>
+          <t>기준치 출처</t>
         </is>
       </c>
       <c r="E66" s="24" t="inlineStr">
         <is>
-          <t>lab|analyzer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F66" s="24" t="inlineStr">
@@ -18271,7 +18267,7 @@
       </c>
       <c r="H66" s="24" t="inlineStr">
         <is>
-          <t>위탁 실험실 [원문 p.38] · 분석기 [원문 발표 p.17] 1개소뿐</t>
+          <t>[설계] [사용자 설정 YYYY-MM-DD] 사업장 허가증 입력값 — 우리가 넣은 값이 아님을 심사자가 바로 알아야 한다. 법령이 원천이므로 우리는 값을 채우지 않는다(설계 명세 색인)</t>
         </is>
       </c>
       <c r="I66" s="8" t="inlineStr">
@@ -18281,7 +18277,7 @@
       </c>
       <c r="J66" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>적용 기준치 패널 출처</t>
         </is>
       </c>
       <c r="K66" s="8" t="inlineStr"/>
@@ -18289,32 +18285,32 @@
     <row r="67" s="35">
       <c r="A67" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-031</t>
+          <t>REQ-AD-011</t>
         </is>
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>SCR-OP-009</t>
+          <t>SCR-OP-004</t>
         </is>
       </c>
       <c r="C67" s="24" t="inlineStr">
         <is>
-          <t>수분석 검증</t>
+          <t>예측</t>
         </is>
       </c>
       <c r="D67" s="24" t="inlineStr">
         <is>
-          <t>발급번호</t>
+          <t>결정계수 R²</t>
         </is>
       </c>
       <c r="E67" s="24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number | null</t>
         </is>
       </c>
       <c r="F67" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0~1</t>
         </is>
       </c>
       <c r="G67" s="24" t="inlineStr">
@@ -18324,7 +18320,7 @@
       </c>
       <c r="H67" s="24" t="inlineStr">
         <is>
-          <t>성적서 체계 [데이터셋 Non_TMS_sites/05]</t>
+          <t>TN·TP만 [원문 p.27] · TOC는 원문에 없어 null [INC-20·21]</t>
         </is>
       </c>
       <c r="I67" s="8" t="inlineStr">
@@ -18337,7 +18333,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K67" s="8" t="inlineStr"/>
+      <c r="K67" s="8" t="inlineStr">
+        <is>
+          <t>INC-20 원문 모순 — 채택안은 출처 열에 적었다</t>
+        </is>
+      </c>
     </row>
     <row r="68" s="35">
       <c r="A68" s="24" t="inlineStr">
@@ -18357,17 +18357,17 @@
       </c>
       <c r="D68" s="24" t="inlineStr">
         <is>
-          <t>접수일 · 시험기간</t>
+          <t>검증 원천</t>
         </is>
       </c>
       <c r="E68" s="24" t="inlineStr">
         <is>
-          <t>ISO8601 · string</t>
+          <t>lab|analyzer</t>
         </is>
       </c>
       <c r="F68" s="24" t="inlineStr">
         <is>
-          <t>KST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G68" s="24" t="inlineStr">
@@ -18377,7 +18377,7 @@
       </c>
       <c r="H68" s="24" t="inlineStr">
         <is>
-          <t>[데이터셋 docs/datasets/Non_TMS_sites] 성적서 항목</t>
+          <t>위탁 실험실 [원문 p.38] · 분석기 [원문 발표 p.17] 1개소뿐</t>
         </is>
       </c>
       <c r="I68" s="8" t="inlineStr">
@@ -18410,7 +18410,7 @@
       </c>
       <c r="D69" s="24" t="inlineStr">
         <is>
-          <t>분석 기관</t>
+          <t>발급번호</t>
         </is>
       </c>
       <c r="E69" s="24" t="inlineStr">
@@ -18430,7 +18430,7 @@
       </c>
       <c r="H69" s="24" t="inlineStr">
         <is>
-          <t>[데이터셋 docs/datasets/Non_TMS_sites] 성적서의 위탁 분석 기관</t>
+          <t>성적서 체계 [데이터셋 Non_TMS_sites/05]</t>
         </is>
       </c>
       <c r="I69" s="8" t="inlineStr">
@@ -18463,7 +18463,7 @@
       </c>
       <c r="D70" s="24" t="inlineStr">
         <is>
-          <t>시료 시각·접수번호</t>
+          <t>접수일 · 시험기간</t>
         </is>
       </c>
       <c r="E70" s="24" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="H70" s="24" t="inlineStr">
         <is>
-          <t>9:45부터 매시 8건 [데이터셋 Non_TMS_sites/05]</t>
+          <t>[데이터셋 docs/datasets/Non_TMS_sites] 성적서 항목</t>
         </is>
       </c>
       <c r="I70" s="8" t="inlineStr">
@@ -18516,17 +18516,17 @@
       </c>
       <c r="D71" s="24" t="inlineStr">
         <is>
-          <t>항목별 실측값</t>
+          <t>분석 기관</t>
         </is>
       </c>
       <c r="E71" s="24" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F71" s="24" t="inlineStr">
         <is>
-          <t>mg/L</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G71" s="24" t="inlineStr">
@@ -18536,7 +18536,7 @@
       </c>
       <c r="H71" s="24" t="inlineStr">
         <is>
-          <t>TOC·TN·TP·SS·COD 5종. 값의 크기는 시연 계열에 맞춘다 [설계] — 형식만 성적서에서 가져왔다</t>
+          <t>[데이터셋 docs/datasets/Non_TMS_sites] 성적서의 위탁 분석 기관</t>
         </is>
       </c>
       <c r="I71" s="8" t="inlineStr">
@@ -18569,27 +18569,27 @@
       </c>
       <c r="D72" s="24" t="inlineStr">
         <is>
-          <t>AI 추정값</t>
+          <t>시료 시각·접수번호</t>
         </is>
       </c>
       <c r="E72" s="24" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>ISO8601 · string</t>
         </is>
       </c>
       <c r="F72" s="24" t="inlineStr">
         <is>
-          <t>mg/L</t>
+          <t>KST</t>
         </is>
       </c>
       <c r="G72" s="24" t="inlineStr">
         <is>
-          <t>[파생: 그 회차 실측 + 시연 오차]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H72" s="24" t="inlineStr">
         <is>
-          <t>[PROVISIONAL] 실제 시스템은 운영 이력에서 그 시각 값을 읽는다(REQ-AD-030 미구현). 오차 폭은 시연값이며 성능 목표가 아니다</t>
+          <t>9:45부터 매시 8건 [데이터셋 Non_TMS_sites/05]</t>
         </is>
       </c>
       <c r="I72" s="8" t="inlineStr">
@@ -18602,11 +18602,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K72" s="8" t="inlineStr">
-        <is>
-          <t>임시값 — 확정 시 src/shared/config/provisional.ts 한 파일을 교체한다</t>
-        </is>
-      </c>
+      <c r="K72" s="8" t="inlineStr"/>
     </row>
     <row r="73" s="35">
       <c r="A73" s="24" t="inlineStr">
@@ -18626,12 +18622,12 @@
       </c>
       <c r="D73" s="24" t="inlineStr">
         <is>
-          <t>오차</t>
+          <t>항목별 실측값</t>
         </is>
       </c>
       <c r="E73" s="24" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>number</t>
         </is>
       </c>
       <c r="F73" s="24" t="inlineStr">
@@ -18641,12 +18637,12 @@
       </c>
       <c r="G73" s="24" t="inlineStr">
         <is>
-          <t>[파생: AI 추정 − 실측]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H73" s="24" t="inlineStr">
         <is>
-          <t>부호가 정보다 — 보정 방향을 정한다 [설계]</t>
+          <t>TOC·TN·TP·SS·COD 5종. 값의 크기는 시연 계열에 맞춘다 [설계] — 형식만 성적서에서 가져왔다</t>
         </is>
       </c>
       <c r="I73" s="8" t="inlineStr">
@@ -18679,27 +18675,27 @@
       </c>
       <c r="D74" s="24" t="inlineStr">
         <is>
-          <t>추정 불가 사유</t>
+          <t>AI 추정값</t>
         </is>
       </c>
       <c r="E74" s="24" t="inlineStr">
         <is>
-          <t>string | null</t>
+          <t>number | null</t>
         </is>
       </c>
       <c r="F74" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="G74" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[파생: 그 회차 실측 + 시연 오차]</t>
         </is>
       </c>
       <c r="H74" s="24" t="inlineStr">
         <is>
-          <t>SS는 계측·추정 대상 아님 [공정자료 p.5·19] · COD는 폐지 [공정자료 p.12·16]</t>
+          <t>[PROVISIONAL] 실제 시스템은 운영 이력에서 그 시각 값을 읽는다(REQ-AD-030 미구현). 오차 폭은 시연값이며 성능 목표가 아니다</t>
         </is>
       </c>
       <c r="I74" s="8" t="inlineStr">
@@ -18712,7 +18708,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K74" s="8" t="inlineStr"/>
+      <c r="K74" s="8" t="inlineStr">
+        <is>
+          <t>임시값 — 확정 시 src/shared/config/provisional.ts 한 파일을 교체한다</t>
+        </is>
+      </c>
     </row>
     <row r="75" s="35">
       <c r="A75" s="24" t="inlineStr">
@@ -18732,7 +18732,7 @@
       </c>
       <c r="D75" s="24" t="inlineStr">
         <is>
-          <t>결정계수 R²</t>
+          <t>오차</t>
         </is>
       </c>
       <c r="E75" s="24" t="inlineStr">
@@ -18742,17 +18742,17 @@
       </c>
       <c r="F75" s="24" t="inlineStr">
         <is>
-          <t>0~1</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="G75" s="24" t="inlineStr">
         <is>
-          <t>[파생: 1 − 잔차제곱합/총제곱합] · 항목별로 계산한다</t>
+          <t>[파생: AI 추정 − 실측]</t>
         </is>
       </c>
       <c r="H75" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.38] · 표본 2개 미만이면 null — 한 점으로 정의되지 않는다(E3) · 모아서 계산하면 항목 간 크기 차이가 R²를 부풀린다</t>
+          <t>부호가 정보다 — 보정 방향을 정한다 [설계]</t>
         </is>
       </c>
       <c r="I75" s="8" t="inlineStr">
@@ -18785,27 +18785,27 @@
       </c>
       <c r="D76" s="24" t="inlineStr">
         <is>
-          <t>평균절대오차 MAE</t>
+          <t>추정 불가 사유</t>
         </is>
       </c>
       <c r="E76" s="24" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>string | null</t>
         </is>
       </c>
       <c r="F76" s="24" t="inlineStr">
         <is>
-          <t>mg/L</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G76" s="24" t="inlineStr">
         <is>
-          <t>[파생: 절대오차 평균]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H76" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.38]</t>
+          <t>SS는 계측·추정 대상 아님 [공정자료 p.5·19] · COD는 폐지 [공정자료 p.12·16]</t>
         </is>
       </c>
       <c r="I76" s="8" t="inlineStr">
@@ -18838,7 +18838,7 @@
       </c>
       <c r="D77" s="24" t="inlineStr">
         <is>
-          <t>제곱평균제곱근오차 RMSE</t>
+          <t>결정계수 R²</t>
         </is>
       </c>
       <c r="E77" s="24" t="inlineStr">
@@ -18848,17 +18848,17 @@
       </c>
       <c r="F77" s="24" t="inlineStr">
         <is>
-          <t>mg/L</t>
+          <t>0~1</t>
         </is>
       </c>
       <c r="G77" s="24" t="inlineStr">
         <is>
-          <t>[파생: 제곱오차 평균의 제곱근]</t>
+          <t>[파생: 1 − 잔차제곱합/총제곱합] · 항목별로 계산한다</t>
         </is>
       </c>
       <c r="H77" s="24" t="inlineStr">
         <is>
-          <t>[원문 발표 p.26 그림] 검증 방법 5단계가 R², MAE/RMSE로 적는다. MAE와 나란히 두어야 오차가 고른지 몇 개가 튀는지 드러난다</t>
+          <t>[원문 p.38] · 표본 2개 미만이면 null — 한 점으로 정의되지 않는다(E3) · 모아서 계산하면 항목 간 크기 차이가 R²를 부풀린다</t>
         </is>
       </c>
       <c r="I77" s="8" t="inlineStr">
@@ -18891,27 +18891,27 @@
       </c>
       <c r="D78" s="24" t="inlineStr">
         <is>
-          <t>표본 수</t>
+          <t>평균절대오차 MAE</t>
         </is>
       </c>
       <c r="E78" s="24" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>number | null</t>
         </is>
       </c>
       <c r="F78" s="24" t="inlineStr">
         <is>
-          <t>쌍</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="G78" s="24" t="inlineStr">
         <is>
-          <t>[파생: 대조 가능한 쌍의 수]</t>
+          <t>[파생: 절대오차 평균]</t>
         </is>
       </c>
       <c r="H78" s="24" t="inlineStr">
         <is>
-          <t>[설계] 값과 함께 다녀야 신뢰도를 읽을 수 있다(E3)</t>
+          <t>[원문 p.38]</t>
         </is>
       </c>
       <c r="I78" s="8" t="inlineStr">
@@ -18929,47 +18929,47 @@
     <row r="79" s="35">
       <c r="A79" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-012</t>
+          <t>REQ-AD-031</t>
         </is>
       </c>
       <c r="B79" s="24" t="inlineStr">
         <is>
-          <t>SCR-OP-005</t>
+          <t>SCR-OP-009</t>
         </is>
       </c>
       <c r="C79" s="24" t="inlineStr">
         <is>
-          <t>설비</t>
+          <t>수분석 검증</t>
         </is>
       </c>
       <c r="D79" s="24" t="inlineStr">
         <is>
-          <t>설비 ID</t>
+          <t>제곱평균제곱근오차 RMSE</t>
         </is>
       </c>
       <c r="E79" s="24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number | null</t>
         </is>
       </c>
       <c r="F79" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="G79" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[파생: 제곱오차 평균의 제곱근]</t>
         </is>
       </c>
       <c r="H79" s="24" t="inlineStr">
         <is>
-          <t>[설계]</t>
+          <t>[원문 발표 p.26 그림] 검증 방법 5단계가 R², MAE/RMSE로 적는다. MAE와 나란히 두어야 오차가 고른지 몇 개가 튀는지 드러난다</t>
         </is>
       </c>
       <c r="I79" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J79" s="8" t="inlineStr">
@@ -18982,42 +18982,42 @@
     <row r="80" s="35">
       <c r="A80" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-012</t>
+          <t>REQ-AD-031</t>
         </is>
       </c>
       <c r="B80" s="24" t="inlineStr">
         <is>
-          <t>SCR-OP-001·005</t>
+          <t>SCR-OP-009</t>
         </is>
       </c>
       <c r="C80" s="24" t="inlineStr">
         <is>
-          <t>설비</t>
+          <t>수분석 검증</t>
         </is>
       </c>
       <c r="D80" s="24" t="inlineStr">
         <is>
-          <t>설비명</t>
+          <t>표본 수</t>
         </is>
       </c>
       <c r="E80" s="24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="F80" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>쌍</t>
         </is>
       </c>
       <c r="G80" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[파생: 대조 가능한 쌍의 수]</t>
         </is>
       </c>
       <c r="H80" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.30] 펌프·폭기장치</t>
+          <t>[설계] 값과 함께 다녀야 신뢰도를 읽을 수 있다(E3)</t>
         </is>
       </c>
       <c r="I80" s="8" t="inlineStr">
@@ -19040,7 +19040,7 @@
       </c>
       <c r="B81" s="24" t="inlineStr">
         <is>
-          <t>SCR-OP-001·005</t>
+          <t>SCR-OP-005</t>
         </is>
       </c>
       <c r="C81" s="24" t="inlineStr">
@@ -19050,17 +19050,17 @@
       </c>
       <c r="D81" s="24" t="inlineStr">
         <is>
-          <t>고장 확률</t>
+          <t>설비 ID</t>
         </is>
       </c>
       <c r="E81" s="24" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F81" s="24" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G81" s="24" t="inlineStr">
@@ -19070,12 +19070,12 @@
       </c>
       <c r="H81" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.66] 0~100%</t>
+          <t>[설계]</t>
         </is>
       </c>
       <c r="I81" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J81" s="8" t="inlineStr">
@@ -19103,17 +19103,17 @@
       </c>
       <c r="D82" s="24" t="inlineStr">
         <is>
-          <t>잔여 수명(RUL)</t>
+          <t>설비명</t>
         </is>
       </c>
       <c r="E82" s="24" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F82" s="24" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G82" s="24" t="inlineStr">
@@ -19123,7 +19123,7 @@
       </c>
       <c r="H82" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.66] · 단위 [PROVISIONAL]</t>
+          <t>[원문 p.30] 펌프·폭기장치 · 대수는 시연값 [TBD-48]</t>
         </is>
       </c>
       <c r="I82" s="8" t="inlineStr">
@@ -19133,19 +19133,19 @@
       </c>
       <c r="J82" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>설비 카드·표</t>
         </is>
       </c>
       <c r="K82" s="8" t="inlineStr">
         <is>
-          <t>임시값 — 확정 시 src/shared/config/provisional.ts 한 파일을 교체한다</t>
+          <t>TBD-48 원문 미확정</t>
         </is>
       </c>
     </row>
     <row r="83" s="35">
       <c r="A83" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-018</t>
+          <t>REQ-AD-012</t>
         </is>
       </c>
       <c r="B83" s="24" t="inlineStr">
@@ -19160,27 +19160,27 @@
       </c>
       <c r="D83" s="24" t="inlineStr">
         <is>
-          <t>MPI</t>
+          <t>가동 여부</t>
         </is>
       </c>
       <c r="E83" s="24" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean|null</t>
         </is>
       </c>
       <c r="F83" s="24" t="inlineStr">
         <is>
-          <t>상대 지수</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G83" s="24" t="inlineStr">
         <is>
-          <t>산식 없음</t>
+          <t>[파생: 마지막 표본 구간의 결측 여부 + 위험도]</t>
         </is>
       </c>
       <c r="H83" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.32] · [TBD-22] 산정식·범위·단위 없음</t>
+          <t>[회의 2026-08-20] on/off만 확인 가능 · null은 모름(E4)</t>
         </is>
       </c>
       <c r="I83" s="8" t="inlineStr">
@@ -19190,14 +19190,10 @@
       </c>
       <c r="J83" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K83" s="8" t="inlineStr">
-        <is>
-          <t>TBD-22 원문 미확정</t>
-        </is>
-      </c>
+          <t>설비 카드 가동 · 표</t>
+        </is>
+      </c>
+      <c r="K83" s="8" t="inlineStr"/>
     </row>
     <row r="84" s="35">
       <c r="A84" s="24" t="inlineStr">
@@ -19207,7 +19203,7 @@
       </c>
       <c r="B84" s="24" t="inlineStr">
         <is>
-          <t>SCR-OP-001·005</t>
+          <t>SCR-OP-005</t>
         </is>
       </c>
       <c r="C84" s="24" t="inlineStr">
@@ -19217,12 +19213,12 @@
       </c>
       <c r="D84" s="24" t="inlineStr">
         <is>
-          <t>상태 등급</t>
+          <t>이상 신호</t>
         </is>
       </c>
       <c r="E84" s="24" t="inlineStr">
         <is>
-          <t>4등급</t>
+          <t>진동|전류 배열</t>
         </is>
       </c>
       <c r="F84" s="24" t="inlineStr">
@@ -19232,12 +19228,12 @@
       </c>
       <c r="G84" s="24" t="inlineStr">
         <is>
-          <t>[파생: toStatusLevel(고장 확률)]</t>
+          <t>[파생: 위험도 × 사업장 세기]</t>
         </is>
       </c>
       <c r="H84" s="24" t="inlineStr">
         <is>
-          <t>[INC-01·03·04]</t>
+          <t>[회의 2026-08-20] 진동 감지 센서 · [원문 발표 p.11·18 그림] 진동 이상 · 사양 미정 [TBD-49]</t>
         </is>
       </c>
       <c r="I84" s="8" t="inlineStr">
@@ -19247,12 +19243,12 @@
       </c>
       <c r="J84" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>설비 카드 이상 신호 · 표</t>
         </is>
       </c>
       <c r="K84" s="8" t="inlineStr">
         <is>
-          <t>INC-01 원문 모순 — 채택안은 출처 열에 적었다</t>
+          <t>TBD-49 원문 미확정</t>
         </is>
       </c>
     </row>
@@ -19274,27 +19270,27 @@
       </c>
       <c r="D85" s="24" t="inlineStr">
         <is>
-          <t>누적 가동시간</t>
+          <t>이상 시작 시각</t>
         </is>
       </c>
       <c r="E85" s="24" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>ISO8601|null</t>
         </is>
       </c>
       <c r="F85" s="24" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>KST</t>
         </is>
       </c>
       <c r="G85" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[파생: 창 끝 − 지속 시간]</t>
         </is>
       </c>
       <c r="H85" s="24" t="inlineStr">
         <is>
-          <t>[설계]</t>
+          <t>[설계] 언제부터인지 없이 이상만 적으면 대응 순서를 못 정한다(E5)</t>
         </is>
       </c>
       <c r="I85" s="8" t="inlineStr">
@@ -19304,7 +19300,7 @@
       </c>
       <c r="J85" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>상세 모달</t>
         </is>
       </c>
       <c r="K85" s="8" t="inlineStr"/>
@@ -19312,7 +19308,7 @@
     <row r="86" s="35">
       <c r="A86" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-019</t>
+          <t>REQ-AD-012</t>
         </is>
       </c>
       <c r="B86" s="24" t="inlineStr">
@@ -19322,32 +19318,32 @@
       </c>
       <c r="C86" s="24" t="inlineStr">
         <is>
-          <t>설비 이력</t>
+          <t>설비</t>
         </is>
       </c>
       <c r="D86" s="24" t="inlineStr">
         <is>
-          <t>며칠 전</t>
+          <t>이상 지속</t>
         </is>
       </c>
       <c r="E86" s="24" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>number|null</t>
         </is>
       </c>
       <c r="F86" s="24" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>시간</t>
         </is>
       </c>
       <c r="G86" s="24" t="inlineStr">
         <is>
-          <t>0이 오늘</t>
+          <t>[파생: 이상 구간 칸 수]</t>
         </is>
       </c>
       <c r="H86" s="24" t="inlineStr">
         <is>
-          <t>[설계]</t>
+          <t>[설계] 등급 판정의 두 축 중 하나 · 모르면 null(E4)</t>
         </is>
       </c>
       <c r="I86" s="8" t="inlineStr">
@@ -19357,7 +19353,7 @@
       </c>
       <c r="J86" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>설비 카드·표·순위</t>
         </is>
       </c>
       <c r="K86" s="8" t="inlineStr"/>
@@ -19365,27 +19361,27 @@
     <row r="87" s="35">
       <c r="A87" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-019</t>
+          <t>REQ-AD-012</t>
         </is>
       </c>
       <c r="B87" s="24" t="inlineStr">
         <is>
-          <t>SCR-OP-005</t>
+          <t>SCR-OP-001·005</t>
         </is>
       </c>
       <c r="C87" s="24" t="inlineStr">
         <is>
-          <t>설비 이력</t>
+          <t>설비</t>
         </is>
       </c>
       <c r="D87" s="24" t="inlineStr">
         <is>
-          <t>날짜</t>
+          <t>상태 등급</t>
         </is>
       </c>
       <c r="E87" s="24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>4등급</t>
         </is>
       </c>
       <c r="F87" s="24" t="inlineStr">
@@ -19395,12 +19391,12 @@
       </c>
       <c r="G87" s="24" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>[파생: toEquipmentStatus(신호 수, 지속)]</t>
         </is>
       </c>
       <c r="H87" s="24" t="inlineStr">
         <is>
-          <t>[설계]</t>
+          <t>[INC-01·03·04] 4단계 · 판정 규칙은 원문에 없다 [TBD-50]</t>
         </is>
       </c>
       <c r="I87" s="8" t="inlineStr">
@@ -19410,15 +19406,19 @@
       </c>
       <c r="J87" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K87" s="8" t="inlineStr"/>
+          <t>등급 배지</t>
+        </is>
+      </c>
+      <c r="K87" s="8" t="inlineStr">
+        <is>
+          <t>TBD-50 원문 미확정 / INC-01 원문 모순 — 채택안은 출처 열에 적었다</t>
+        </is>
+      </c>
     </row>
     <row r="88" s="35">
       <c r="A88" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-019</t>
+          <t>REQ-AD-012</t>
         </is>
       </c>
       <c r="B88" s="24" t="inlineStr">
@@ -19428,12 +19428,12 @@
       </c>
       <c r="C88" s="24" t="inlineStr">
         <is>
-          <t>설비 이력</t>
+          <t>설비</t>
         </is>
       </c>
       <c r="D88" s="24" t="inlineStr">
         <is>
-          <t>그날의 잔여 수명</t>
+          <t>누적 가동시간</t>
         </is>
       </c>
       <c r="E88" s="24" t="inlineStr">
@@ -19443,17 +19443,17 @@
       </c>
       <c r="F88" s="24" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>h</t>
         </is>
       </c>
       <c r="G88" s="24" t="inlineStr">
         <is>
-          <t>[파생: 현재 RUL + Σ(일일감소 × 0.55~1.45)] · 일일감소 = 1 + 고장확률/100 × 0.9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H88" s="24" t="inlineStr">
         <is>
-          <t>[PROVISIONAL] 감소 폭에 원문 근거 없음</t>
+          <t>[설계]</t>
         </is>
       </c>
       <c r="I88" s="8" t="inlineStr">
@@ -19463,14 +19463,10 @@
       </c>
       <c r="J88" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K88" s="8" t="inlineStr">
-        <is>
-          <t>임시값 — 확정 시 src/shared/config/provisional.ts 한 파일을 교체한다</t>
-        </is>
-      </c>
+          <t>설비 표</t>
+        </is>
+      </c>
+      <c r="K88" s="8" t="inlineStr"/>
     </row>
     <row r="89" s="35">
       <c r="A89" s="24" t="inlineStr">
@@ -19490,7 +19486,7 @@
       </c>
       <c r="D89" s="24" t="inlineStr">
         <is>
-          <t>시점(오늘 기준)</t>
+          <t>격자 칸(시각)</t>
         </is>
       </c>
       <c r="E89" s="24" t="inlineStr">
@@ -19500,17 +19496,17 @@
       </c>
       <c r="F89" s="24" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>시</t>
         </is>
       </c>
       <c r="G89" s="24" t="inlineStr">
         <is>
-          <t>음수=지나온 날 · 0=오늘 · 양수=앞날</t>
+          <t>0이 창의 시작. 24칸</t>
         </is>
       </c>
       <c r="H89" s="24" t="inlineStr">
         <is>
-          <t>[설계]</t>
+          <t>[원문 발표 p.18 그림] 00시~24시</t>
         </is>
       </c>
       <c r="I89" s="8" t="inlineStr">
@@ -19520,7 +19516,7 @@
       </c>
       <c r="J89" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>가동 격자 열</t>
         </is>
       </c>
       <c r="K89" s="8" t="inlineStr"/>
@@ -19543,7 +19539,7 @@
       </c>
       <c r="D90" s="24" t="inlineStr">
         <is>
-          <t>예측 계열 날짜</t>
+          <t>격자 칸 시각</t>
         </is>
       </c>
       <c r="E90" s="24" t="inlineStr">
@@ -19553,12 +19549,12 @@
       </c>
       <c r="F90" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>KST</t>
         </is>
       </c>
       <c r="G90" s="24" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>칸 첫 표본의 시각</t>
         </is>
       </c>
       <c r="H90" s="24" t="inlineStr">
@@ -19573,7 +19569,7 @@
       </c>
       <c r="J90" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>격자 눈금·툴팁</t>
         </is>
       </c>
       <c r="K90" s="8" t="inlineStr"/>
@@ -19596,27 +19592,27 @@
       </c>
       <c r="D91" s="24" t="inlineStr">
         <is>
-          <t>지나온 값</t>
+          <t>칸 가동 여부</t>
         </is>
       </c>
       <c r="E91" s="24" t="inlineStr">
         <is>
-          <t>number|null</t>
+          <t>boolean|null</t>
         </is>
       </c>
       <c r="F91" s="24" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G91" s="24" t="inlineStr">
         <is>
-          <t>앞날은 null</t>
+          <t>[파생: 한 시간 안에 결측이 하나라도 있으면 null]</t>
         </is>
       </c>
       <c r="H91" s="24" t="inlineStr">
         <is>
-          <t>[설계]</t>
+          <t>[회의 2026-08-20] · 결측을 정지로 적으면 가동률이 틀린다(E4)</t>
         </is>
       </c>
       <c r="I91" s="8" t="inlineStr">
@@ -19626,7 +19622,7 @@
       </c>
       <c r="J91" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>격자 칸 색</t>
         </is>
       </c>
       <c r="K91" s="8" t="inlineStr"/>
@@ -19649,27 +19645,27 @@
       </c>
       <c r="D92" s="24" t="inlineStr">
         <is>
-          <t>추세 외삽</t>
+          <t>칸 이상 신호</t>
         </is>
       </c>
       <c r="E92" s="24" t="inlineStr">
         <is>
-          <t>number|null</t>
+          <t>진동|전류 배열</t>
         </is>
       </c>
       <c r="F92" s="24" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G92" s="24" t="inlineStr">
         <is>
-          <t>[파생: max(0, 현재 RUL − 경과일 × 일일감소)] · 모델 산출 아님</t>
+          <t>[파생: 이상 구간 안이면 현재 신호]</t>
         </is>
       </c>
       <c r="H92" s="24" t="inlineStr">
         <is>
-          <t>[설계] [TBD-22]</t>
+          <t>[설계] 시간마다 다른 신호를 만들 근거가 없다</t>
         </is>
       </c>
       <c r="I92" s="8" t="inlineStr">
@@ -19679,14 +19675,10 @@
       </c>
       <c r="J92" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K92" s="8" t="inlineStr">
-        <is>
-          <t>TBD-22 원문 미확정</t>
-        </is>
-      </c>
+          <t>격자 칸 글리프</t>
+        </is>
+      </c>
+      <c r="K92" s="8" t="inlineStr"/>
     </row>
     <row r="93" s="35">
       <c r="A93" s="24" t="inlineStr">
@@ -19706,27 +19698,27 @@
       </c>
       <c r="D93" s="24" t="inlineStr">
         <is>
-          <t>0 도달 예상</t>
+          <t>방지시설 줄 시각</t>
         </is>
       </c>
       <c r="E93" s="24" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F93" s="24" t="inlineStr">
         <is>
-          <t>일 후</t>
+          <t>KST</t>
         </is>
       </c>
       <c r="G93" s="24" t="inlineStr">
         <is>
-          <t>[파생: round(현재 RUL ÷ 일일감소)] · 최소 1</t>
+          <t>설비 격자와 같은 축</t>
         </is>
       </c>
       <c r="H93" s="24" t="inlineStr">
         <is>
-          <t>[설계] RandomForest는 확률만 낸다 [원문 p.66]</t>
+          <t>[설계]</t>
         </is>
       </c>
       <c r="I93" s="8" t="inlineStr">
@@ -19736,7 +19728,7 @@
       </c>
       <c r="J93" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>방지시설 줄</t>
         </is>
       </c>
       <c r="K93" s="8" t="inlineStr"/>
@@ -19759,27 +19751,27 @@
       </c>
       <c r="D94" s="24" t="inlineStr">
         <is>
-          <t>격자 칸(시각)</t>
+          <t>방지시설 미가동</t>
         </is>
       </c>
       <c r="E94" s="24" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean|null</t>
         </is>
       </c>
       <c r="F94" s="24" t="inlineStr">
         <is>
-          <t>시</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G94" s="24" t="inlineStr">
         <is>
-          <t>0이 창의 시작. 24칸</t>
+          <t>[파생: isTreatmentIdleAt를 시간 단위로 묶음]</t>
         </is>
       </c>
       <c r="H94" s="24" t="inlineStr">
         <is>
-          <t>[원문 발표 p.18 그림] 00시~24시</t>
+          <t>[TBD-46] · 설비 칸과 다른 축이라 섞지 않는다</t>
         </is>
       </c>
       <c r="I94" s="8" t="inlineStr">
@@ -19789,30 +19781,34 @@
       </c>
       <c r="J94" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K94" s="8" t="inlineStr"/>
+          <t>방지시설 줄</t>
+        </is>
+      </c>
+      <c r="K94" s="8" t="inlineStr">
+        <is>
+          <t>TBD-46 원문 미확정</t>
+        </is>
+      </c>
     </row>
     <row r="95" s="35">
       <c r="A95" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-019</t>
+          <t>REQ-AD-024</t>
         </is>
       </c>
       <c r="B95" s="24" t="inlineStr">
         <is>
-          <t>SCR-OP-005</t>
+          <t>SCR-OP-007</t>
         </is>
       </c>
       <c r="C95" s="24" t="inlineStr">
         <is>
-          <t>설비 이력</t>
+          <t>알람</t>
         </is>
       </c>
       <c r="D95" s="24" t="inlineStr">
         <is>
-          <t>격자 칸 시각</t>
+          <t>알람 ID</t>
         </is>
       </c>
       <c r="E95" s="24" t="inlineStr">
@@ -19822,12 +19818,12 @@
       </c>
       <c r="F95" s="24" t="inlineStr">
         <is>
-          <t>KST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G95" s="24" t="inlineStr">
         <is>
-          <t>칸 첫 표본의 시각</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H95" s="24" t="inlineStr">
@@ -19837,7 +19833,7 @@
       </c>
       <c r="I95" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J95" s="8" t="inlineStr">
@@ -19850,27 +19846,27 @@
     <row r="96" s="35">
       <c r="A96" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-019</t>
+          <t>REQ-AD-024</t>
         </is>
       </c>
       <c r="B96" s="24" t="inlineStr">
         <is>
-          <t>SCR-OP-005</t>
+          <t>SCR-OP-007</t>
         </is>
       </c>
       <c r="C96" s="24" t="inlineStr">
         <is>
-          <t>설비 이력</t>
+          <t>알람</t>
         </is>
       </c>
       <c r="D96" s="24" t="inlineStr">
         <is>
-          <t>칸 상태 등급</t>
+          <t>사업장 ID·명</t>
         </is>
       </c>
       <c r="E96" s="24" t="inlineStr">
         <is>
-          <t>4등급|null</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F96" s="24" t="inlineStr">
@@ -19880,12 +19876,12 @@
       </c>
       <c r="G96" s="24" t="inlineStr">
         <is>
-          <t>[파생: toStatusLevel(고장확률 × (0.55 + 진행도 × 0.45))] · 마지막 칸은 현재 고장 확률 그대로</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H96" s="24" t="inlineStr">
         <is>
-          <t>[INC-01·03·04] · null=결측(E4)</t>
+          <t>[설계]</t>
         </is>
       </c>
       <c r="I96" s="8" t="inlineStr">
@@ -19898,51 +19894,47 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K96" s="8" t="inlineStr">
-        <is>
-          <t>INC-01 원문 모순 — 채택안은 출처 열에 적었다</t>
-        </is>
-      </c>
+      <c r="K96" s="8" t="inlineStr"/>
     </row>
     <row r="97" s="35">
       <c r="A97" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-019</t>
+          <t>REQ-AD-024</t>
         </is>
       </c>
       <c r="B97" s="24" t="inlineStr">
         <is>
-          <t>SCR-OP-005</t>
+          <t>SCR-OP-007</t>
         </is>
       </c>
       <c r="C97" s="24" t="inlineStr">
         <is>
-          <t>설비 이력</t>
+          <t>알람</t>
         </is>
       </c>
       <c r="D97" s="24" t="inlineStr">
         <is>
-          <t>방지시설 줄 시각</t>
+          <t>상태 등급</t>
         </is>
       </c>
       <c r="E97" s="24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>4등급</t>
         </is>
       </c>
       <c r="F97" s="24" t="inlineStr">
         <is>
-          <t>KST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G97" s="24" t="inlineStr">
         <is>
-          <t>설비 격자와 같은 축</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H97" s="24" t="inlineStr">
         <is>
-          <t>[설계]</t>
+          <t>[원문 발표 p.15·18·20 그림] — 우선순위와 다른 축이다(p.20이 둘을 다른 열로 보여준다)</t>
         </is>
       </c>
       <c r="I97" s="8" t="inlineStr">
@@ -19960,27 +19952,27 @@
     <row r="98" s="35">
       <c r="A98" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-019</t>
+          <t>REQ-AD-024</t>
         </is>
       </c>
       <c r="B98" s="24" t="inlineStr">
         <is>
-          <t>SCR-OP-005</t>
+          <t>SCR-OP-001·007</t>
         </is>
       </c>
       <c r="C98" s="24" t="inlineStr">
         <is>
-          <t>설비 이력</t>
+          <t>알람</t>
         </is>
       </c>
       <c r="D98" s="24" t="inlineStr">
         <is>
-          <t>방지시설 미가동</t>
+          <t>우선순위</t>
         </is>
       </c>
       <c r="E98" s="24" t="inlineStr">
         <is>
-          <t>boolean|null</t>
+          <t>urgent|caution|info</t>
         </is>
       </c>
       <c r="F98" s="24" t="inlineStr">
@@ -19990,12 +19982,12 @@
       </c>
       <c r="G98" s="24" t="inlineStr">
         <is>
-          <t>[파생: isTreatmentIdleAt를 시간 단위로 묶음] · 한 표본이라도 모르면 null</t>
+          <t>[파생: PRIORITY_BY_LEVEL[등급]]</t>
         </is>
       </c>
       <c r="H98" s="24" t="inlineStr">
         <is>
-          <t>[TBD-46] 무단 여부는 판정하지 않는다</t>
+          <t>[원문 p.32] 긴급/주의/정보 · 대응 규칙은 원문에 없어 추정이다 [INC-02] (추정으로 등록해 둔 항목이다)</t>
         </is>
       </c>
       <c r="I98" s="8" t="inlineStr">
@@ -20010,7 +20002,7 @@
       </c>
       <c r="K98" s="8" t="inlineStr">
         <is>
-          <t>TBD-46 원문 미확정</t>
+          <t>INC-02 원문 모순 — 채택안은 출처 열에 적었다</t>
         </is>
       </c>
     </row>
@@ -20032,12 +20024,12 @@
       </c>
       <c r="D99" s="24" t="inlineStr">
         <is>
-          <t>알람 ID</t>
+          <t>발생 조건</t>
         </is>
       </c>
       <c r="E99" s="24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>4종 열거</t>
         </is>
       </c>
       <c r="F99" s="24" t="inlineStr">
@@ -20052,12 +20044,12 @@
       </c>
       <c r="H99" s="24" t="inlineStr">
         <is>
-          <t>[설계]</t>
+          <t>[원문 p.32] 이상 탐지/오염도 급변/수질 변화 이상/설비 이상</t>
         </is>
       </c>
       <c r="I99" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J99" s="8" t="inlineStr">
@@ -20085,12 +20077,12 @@
       </c>
       <c r="D100" s="24" t="inlineStr">
         <is>
-          <t>사업장 ID·명</t>
+          <t>처리 상태</t>
         </is>
       </c>
       <c r="E100" s="24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>open|acknowledged|resolved</t>
         </is>
       </c>
       <c r="F100" s="24" t="inlineStr">
@@ -20105,7 +20097,7 @@
       </c>
       <c r="H100" s="24" t="inlineStr">
         <is>
-          <t>[설계]</t>
+          <t>[설계] 원문에 상태 정의 없음</t>
         </is>
       </c>
       <c r="I100" s="8" t="inlineStr">
@@ -20128,7 +20120,7 @@
       </c>
       <c r="B101" s="24" t="inlineStr">
         <is>
-          <t>SCR-OP-007</t>
+          <t>SCR-OP-001·007</t>
         </is>
       </c>
       <c r="C101" s="24" t="inlineStr">
@@ -20138,12 +20130,12 @@
       </c>
       <c r="D101" s="24" t="inlineStr">
         <is>
-          <t>상태 등급</t>
+          <t>제목</t>
         </is>
       </c>
       <c r="E101" s="24" t="inlineStr">
         <is>
-          <t>4등급</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F101" s="24" t="inlineStr">
@@ -20158,7 +20150,7 @@
       </c>
       <c r="H101" s="24" t="inlineStr">
         <is>
-          <t>[원문 발표 p.15·18·20 그림] — 우선순위와 다른 축이다(p.20이 둘을 다른 열로 보여준다)</t>
+          <t>[설계]</t>
         </is>
       </c>
       <c r="I101" s="8" t="inlineStr">
@@ -20181,7 +20173,7 @@
       </c>
       <c r="B102" s="24" t="inlineStr">
         <is>
-          <t>SCR-OP-001·007</t>
+          <t>SCR-OP-007</t>
         </is>
       </c>
       <c r="C102" s="24" t="inlineStr">
@@ -20191,12 +20183,12 @@
       </c>
       <c r="D102" s="24" t="inlineStr">
         <is>
-          <t>우선순위</t>
+          <t>상세</t>
         </is>
       </c>
       <c r="E102" s="24" t="inlineStr">
         <is>
-          <t>urgent|caution|info</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F102" s="24" t="inlineStr">
@@ -20206,12 +20198,12 @@
       </c>
       <c r="G102" s="24" t="inlineStr">
         <is>
-          <t>[파생: PRIORITY_BY_LEVEL[등급]]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H102" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.32] 긴급/주의/정보 · 대응 규칙은 원문에 없어 추정이다 [INC-02] (추정으로 등록해 둔 항목이다)</t>
+          <t>[설계]</t>
         </is>
       </c>
       <c r="I102" s="8" t="inlineStr">
@@ -20224,11 +20216,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K102" s="8" t="inlineStr">
-        <is>
-          <t>INC-02 원문 모순 — 채택안은 출처 열에 적었다</t>
-        </is>
-      </c>
+      <c r="K102" s="8" t="inlineStr"/>
     </row>
     <row r="103" s="35">
       <c r="A103" s="24" t="inlineStr">
@@ -20248,17 +20236,17 @@
       </c>
       <c r="D103" s="24" t="inlineStr">
         <is>
-          <t>발생 조건</t>
+          <t>발생 시각</t>
         </is>
       </c>
       <c r="E103" s="24" t="inlineStr">
         <is>
-          <t>4종 열거</t>
+          <t>ISO8601</t>
         </is>
       </c>
       <c r="F103" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>KST</t>
         </is>
       </c>
       <c r="G103" s="24" t="inlineStr">
@@ -20268,7 +20256,7 @@
       </c>
       <c r="H103" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.32] 이상 탐지/오염도 급변/수질 변화 이상/설비 이상</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="I103" s="8" t="inlineStr">
@@ -20301,27 +20289,27 @@
       </c>
       <c r="D104" s="24" t="inlineStr">
         <is>
-          <t>처리 상태</t>
+          <t>미확인 건수</t>
         </is>
       </c>
       <c r="E104" s="24" t="inlineStr">
         <is>
-          <t>open|acknowledged|resolved</t>
+          <t>number</t>
         </is>
       </c>
       <c r="F104" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>건</t>
         </is>
       </c>
       <c r="G104" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[파생: state === 'open' 개수]</t>
         </is>
       </c>
       <c r="H104" s="24" t="inlineStr">
         <is>
-          <t>[설계] 원문에 상태 정의 없음</t>
+          <t>[설계]</t>
         </is>
       </c>
       <c r="I104" s="8" t="inlineStr">
@@ -20339,32 +20327,32 @@
     <row r="105" s="35">
       <c r="A105" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-024</t>
+          <t>REQ-AD-015</t>
         </is>
       </c>
       <c r="B105" s="24" t="inlineStr">
         <is>
-          <t>SCR-OP-001·007</t>
+          <t>SCR-OP-006</t>
         </is>
       </c>
       <c r="C105" s="24" t="inlineStr">
         <is>
-          <t>알람</t>
+          <t>운영 최적화</t>
         </is>
       </c>
       <c r="D105" s="24" t="inlineStr">
         <is>
-          <t>제목</t>
+          <t>현재 주입량</t>
         </is>
       </c>
       <c r="E105" s="24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="F105" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>L/h</t>
         </is>
       </c>
       <c r="G105" s="24" t="inlineStr">
@@ -20374,7 +20362,7 @@
       </c>
       <c r="H105" s="24" t="inlineStr">
         <is>
-          <t>[설계]</t>
+          <t>[PROVISIONAL, TBD-31] 단위·범위 없음</t>
         </is>
       </c>
       <c r="I105" s="8" t="inlineStr">
@@ -20387,47 +20375,51 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K105" s="8" t="inlineStr"/>
+      <c r="K105" s="8" t="inlineStr">
+        <is>
+          <t>임시값 — 확정 시 src/shared/config/provisional.ts 한 파일을 교체한다 / TBD-31 원문 미확정</t>
+        </is>
+      </c>
     </row>
     <row r="106" s="35">
       <c r="A106" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-024</t>
+          <t>REQ-AD-015</t>
         </is>
       </c>
       <c r="B106" s="24" t="inlineStr">
         <is>
-          <t>SCR-OP-007</t>
+          <t>SCR-OP-006</t>
         </is>
       </c>
       <c r="C106" s="24" t="inlineStr">
         <is>
-          <t>알람</t>
+          <t>운영 최적화</t>
         </is>
       </c>
       <c r="D106" s="24" t="inlineStr">
         <is>
-          <t>상세</t>
+          <t>권장 주입량</t>
         </is>
       </c>
       <c r="E106" s="24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="F106" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>L/h</t>
         </is>
       </c>
       <c r="G106" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[파생: 현재 × (1 − 절감률)]</t>
         </is>
       </c>
       <c r="H106" s="24" t="inlineStr">
         <is>
-          <t>[설계]</t>
+          <t>[원문 p.32·67]</t>
         </is>
       </c>
       <c r="I106" s="8" t="inlineStr">
@@ -20445,32 +20437,32 @@
     <row r="107" s="35">
       <c r="A107" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-024</t>
+          <t>REQ-AD-015</t>
         </is>
       </c>
       <c r="B107" s="24" t="inlineStr">
         <is>
-          <t>SCR-OP-007</t>
+          <t>SCR-OP-006</t>
         </is>
       </c>
       <c r="C107" s="24" t="inlineStr">
         <is>
-          <t>알람</t>
+          <t>운영 최적화</t>
         </is>
       </c>
       <c r="D107" s="24" t="inlineStr">
         <is>
-          <t>발생 시각</t>
+          <t>주입량 단위</t>
         </is>
       </c>
       <c r="E107" s="24" t="inlineStr">
         <is>
-          <t>ISO8601</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F107" s="24" t="inlineStr">
         <is>
-          <t>KST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G107" s="24" t="inlineStr">
@@ -20480,7 +20472,7 @@
       </c>
       <c r="H107" s="24" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>[PROVISIONAL, TBD-31] 원문에 단위가 없다. provisional.ts가 유일한 실체</t>
         </is>
       </c>
       <c r="I107" s="8" t="inlineStr">
@@ -20493,27 +20485,31 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K107" s="8" t="inlineStr"/>
+      <c r="K107" s="8" t="inlineStr">
+        <is>
+          <t>임시값 — 확정 시 src/shared/config/provisional.ts 한 파일을 교체한다 / TBD-31 원문 미확정</t>
+        </is>
+      </c>
     </row>
     <row r="108" s="35">
       <c r="A108" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-024</t>
+          <t>REQ-AD-015</t>
         </is>
       </c>
       <c r="B108" s="24" t="inlineStr">
         <is>
-          <t>SCR-OP-007</t>
+          <t>SCR-OP-006</t>
         </is>
       </c>
       <c r="C108" s="24" t="inlineStr">
         <is>
-          <t>알람</t>
+          <t>운영 최적화</t>
         </is>
       </c>
       <c r="D108" s="24" t="inlineStr">
         <is>
-          <t>미확인 건수</t>
+          <t>약품 절감률</t>
         </is>
       </c>
       <c r="E108" s="24" t="inlineStr">
@@ -20523,17 +20519,17 @@
       </c>
       <c r="F108" s="24" t="inlineStr">
         <is>
-          <t>건</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G108" s="24" t="inlineStr">
         <is>
-          <t>[파생: state === 'open' 개수]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H108" s="24" t="inlineStr">
         <is>
-          <t>[설계]</t>
+          <t>[원문 p.27·31] 검증 수준 20~30%</t>
         </is>
       </c>
       <c r="I108" s="8" t="inlineStr">
@@ -20566,17 +20562,17 @@
       </c>
       <c r="D109" s="24" t="inlineStr">
         <is>
-          <t>현재 주입량</t>
+          <t>권장 근거</t>
         </is>
       </c>
       <c r="E109" s="24" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string[]</t>
         </is>
       </c>
       <c r="F109" s="24" t="inlineStr">
         <is>
-          <t>L/h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G109" s="24" t="inlineStr">
@@ -20586,7 +20582,7 @@
       </c>
       <c r="H109" s="24" t="inlineStr">
         <is>
-          <t>[PROVISIONAL, TBD-31] 단위·범위 없음</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="I109" s="8" t="inlineStr">
@@ -20599,16 +20595,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K109" s="8" t="inlineStr">
-        <is>
-          <t>임시값 — 확정 시 src/shared/config/provisional.ts 한 파일을 교체한다 / TBD-31 원문 미확정</t>
-        </is>
-      </c>
+      <c r="K109" s="8" t="inlineStr"/>
     </row>
     <row r="110" s="35">
       <c r="A110" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-015</t>
+          <t>REQ-AD-016</t>
         </is>
       </c>
       <c r="B110" s="24" t="inlineStr">
@@ -20623,27 +20615,27 @@
       </c>
       <c r="D110" s="24" t="inlineStr">
         <is>
-          <t>권장 주입량</t>
+          <t>조정 대상 변수</t>
         </is>
       </c>
       <c r="E110" s="24" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F110" s="24" t="inlineStr">
         <is>
-          <t>L/h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G110" s="24" t="inlineStr">
         <is>
-          <t>[파생: 현재 × (1 − 절감률)]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H110" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.32·67]</t>
+          <t>[원문 p.67] 최적 설비 운전 조건 (폭기량, 펌프 속도 등)</t>
         </is>
       </c>
       <c r="I110" s="8" t="inlineStr">
@@ -20653,7 +20645,7 @@
       </c>
       <c r="J110" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>운전 조건 행 머리</t>
         </is>
       </c>
       <c r="K110" s="8" t="inlineStr"/>
@@ -20661,7 +20653,7 @@
     <row r="111" s="35">
       <c r="A111" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-015</t>
+          <t>REQ-AD-016</t>
         </is>
       </c>
       <c r="B111" s="24" t="inlineStr">
@@ -20676,7 +20668,7 @@
       </c>
       <c r="D111" s="24" t="inlineStr">
         <is>
-          <t>주입량 단위</t>
+          <t>조정 대상 설비</t>
         </is>
       </c>
       <c r="E111" s="24" t="inlineStr">
@@ -20696,7 +20688,7 @@
       </c>
       <c r="H111" s="24" t="inlineStr">
         <is>
-          <t>[PROVISIONAL, TBD-31] 원문에 단위가 없다. provisional.ts가 유일한 실체</t>
+          <t>[원문 p.30·62·63] 펌프·폭기장치·약품주입펌프 — 종류만 있고 대수는 없다 [TBD-48]</t>
         </is>
       </c>
       <c r="I111" s="8" t="inlineStr">
@@ -20706,19 +20698,19 @@
       </c>
       <c r="J111" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>같은 행</t>
         </is>
       </c>
       <c r="K111" s="8" t="inlineStr">
         <is>
-          <t>임시값 — 확정 시 src/shared/config/provisional.ts 한 파일을 교체한다 / TBD-31 원문 미확정</t>
+          <t>TBD-48 원문 미확정</t>
         </is>
       </c>
     </row>
     <row r="112" s="35">
       <c r="A112" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-015</t>
+          <t>REQ-AD-016</t>
         </is>
       </c>
       <c r="B112" s="24" t="inlineStr">
@@ -20733,7 +20725,7 @@
       </c>
       <c r="D112" s="24" t="inlineStr">
         <is>
-          <t>약품 절감률</t>
+          <t>조정 폭</t>
         </is>
       </c>
       <c r="E112" s="24" t="inlineStr">
@@ -20748,12 +20740,12 @@
       </c>
       <c r="G112" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[파생: (최근 1시간 평균 / 직전 5시간 평균 − 1) × 100 × 배율 × 부호] · 주입 속도는 [파생: −권장 주입량 절감률]</t>
         </is>
       </c>
       <c r="H112" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.27·31] 검증 수준 20~30%</t>
+          <t>방향은 원문 인과 — 폭기량 감소 → DO 저하 → 질산화 저해 → TN 증가 [원문 p.24·62] · 크기는 [PROVISIONAL] PROVISIONAL_OPERATING_GAIN — 원문이 "몇 %"를 주지 않는다 · 절대 단위 [TBD]라 상대 변화만 · 상한 20% [설계: 계측이 튀는 순간 +180%가 나오면 그것이 곧 안전 문제다. 제어는 하지 않지만(REQ-CO-002 미구현) 사람이 따라 한다]</t>
         </is>
       </c>
       <c r="I112" s="8" t="inlineStr">
@@ -20763,15 +20755,19 @@
       </c>
       <c r="J112" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K112" s="8" t="inlineStr"/>
+          <t>양방향 막대 · 수치</t>
+        </is>
+      </c>
+      <c r="K112" s="8" t="inlineStr">
+        <is>
+          <t>임시값 — 확정 시 src/shared/config/provisional.ts 한 파일을 교체한다 / TBD 원문 미확정</t>
+        </is>
+      </c>
     </row>
     <row r="113" s="35">
       <c r="A113" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-015</t>
+          <t>REQ-AD-016</t>
         </is>
       </c>
       <c r="B113" s="24" t="inlineStr">
@@ -20786,27 +20782,27 @@
       </c>
       <c r="D113" s="24" t="inlineStr">
         <is>
-          <t>권장 근거</t>
+          <t>관측값</t>
         </is>
       </c>
       <c r="E113" s="24" t="inlineStr">
         <is>
-          <t>string[]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F113" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>항목 단위</t>
         </is>
       </c>
       <c r="G113" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[파생: 그 항목의 최근·직전 구간 평균]</t>
         </is>
       </c>
       <c r="H113" s="24" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E3 계측을 근거로 말하려면 그 값이 화면에 있어야 한다 — 예전에는 조정 이유가 사업장·시각과 무관한 고정 문장이라 계측을 본 판단처럼 읽혔다 [사용자 지적 2026-08-21]</t>
         </is>
       </c>
       <c r="I113" s="8" t="inlineStr">
@@ -20816,7 +20812,7 @@
       </c>
       <c r="J113" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>운전 조건 행 둘째 줄</t>
         </is>
       </c>
       <c r="K113" s="8" t="inlineStr"/>
@@ -20839,7 +20835,7 @@
       </c>
       <c r="D114" s="24" t="inlineStr">
         <is>
-          <t>조정 대상 변수</t>
+          <t>조정 이유</t>
         </is>
       </c>
       <c r="E114" s="24" t="inlineStr">
@@ -20859,7 +20855,7 @@
       </c>
       <c r="H114" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.67] 폭기량·펌프 속도</t>
+          <t>E3 방향의 근거를 태그와 함께 적는다 — [원문 p.24·62](폭기) · [설계](펌프) · [TBD-51](주입)</t>
         </is>
       </c>
       <c r="I114" s="8" t="inlineStr">
@@ -20869,10 +20865,14 @@
       </c>
       <c r="J114" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K114" s="8" t="inlineStr"/>
+          <t>운전 조건 행 셋째 줄</t>
+        </is>
+      </c>
+      <c r="K114" s="8" t="inlineStr">
+        <is>
+          <t>TBD-51 원문 미확정</t>
+        </is>
+      </c>
     </row>
     <row r="115" s="35">
       <c r="A115" s="24" t="inlineStr">
@@ -20892,37 +20892,37 @@
       </c>
       <c r="D115" s="24" t="inlineStr">
         <is>
-          <t>조정 대상 설비</t>
+          <t>계측 신호</t>
         </is>
       </c>
       <c r="E115" s="24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>OperatingSignals</t>
         </is>
       </c>
       <c r="F115" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>항목 단위</t>
         </is>
       </c>
       <c r="G115" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[파생: DO·유량의 최근 1시간 vs 직전 5시간 평균과 그 비율]</t>
         </is>
       </c>
       <c r="H115" s="24" t="inlineStr">
         <is>
-          <t>[설계]</t>
+          <t>[설계] 위젯이 계산해 넣는다 — 계열은 measurement의 것이고 slice끼리 참조하지 않는다(FSD ). 에너지 효율의 현재값을 넘겨받는 것과 같은 구조 · 넘기지 않으면 운전 조건을 만들지 않는다(E4)</t>
         </is>
       </c>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J115" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>내부</t>
         </is>
       </c>
       <c r="K115" s="8" t="inlineStr"/>
@@ -20930,7 +20930,7 @@
     <row r="116" s="35">
       <c r="A116" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-016</t>
+          <t>REQ-AD-017</t>
         </is>
       </c>
       <c r="B116" s="24" t="inlineStr">
@@ -20945,27 +20945,27 @@
       </c>
       <c r="D116" s="24" t="inlineStr">
         <is>
-          <t>조정 폭</t>
+          <t>현재 에너지 효율</t>
         </is>
       </c>
       <c r="E116" s="24" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>number | null</t>
         </is>
       </c>
       <c r="F116" s="24" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kWh/m³</t>
         </is>
       </c>
       <c r="G116" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[파생: 평균전력 × 24 ÷ 평균유량]</t>
         </is>
       </c>
       <c r="H116" s="24" t="inlineStr">
         <is>
-          <t>절대 단위 [TBD] — 상대 변화만</t>
+          <t>[원문 p.67] 단위</t>
         </is>
       </c>
       <c r="I116" s="8" t="inlineStr">
@@ -20978,16 +20978,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K116" s="8" t="inlineStr">
-        <is>
-          <t>TBD 원문 미확정</t>
-        </is>
-      </c>
+      <c r="K116" s="8" t="inlineStr"/>
     </row>
     <row r="117" s="35">
       <c r="A117" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-016</t>
+          <t>REQ-AD-017</t>
         </is>
       </c>
       <c r="B117" s="24" t="inlineStr">
@@ -21002,27 +20998,27 @@
       </c>
       <c r="D117" s="24" t="inlineStr">
         <is>
-          <t>조정 이유</t>
+          <t>목표 에너지 효율</t>
         </is>
       </c>
       <c r="E117" s="24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number | null</t>
         </is>
       </c>
       <c r="F117" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>kWh/m³</t>
         </is>
       </c>
       <c r="G117" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[파생: 현재 × (1 − 10%)]</t>
         </is>
       </c>
       <c r="H117" s="24" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>[원문 p.27·64]</t>
         </is>
       </c>
       <c r="I117" s="8" t="inlineStr">
@@ -21055,27 +21051,27 @@
       </c>
       <c r="D118" s="24" t="inlineStr">
         <is>
-          <t>현재 에너지 효율</t>
+          <t>에너지 절감률</t>
         </is>
       </c>
       <c r="E118" s="24" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>number</t>
         </is>
       </c>
       <c r="F118" s="24" t="inlineStr">
         <is>
-          <t>kWh/m³</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G118" s="24" t="inlineStr">
         <is>
-          <t>[파생: 평균전력 × 24 ÷ 평균유량]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H118" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.67] 단위</t>
+          <t>[원문 p.27·64] ≥10%</t>
         </is>
       </c>
       <c r="I118" s="8" t="inlineStr">
@@ -21093,7 +21089,7 @@
     <row r="119" s="35">
       <c r="A119" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-017</t>
+          <t>REQ-AD-005</t>
         </is>
       </c>
       <c r="B119" s="24" t="inlineStr">
@@ -21108,27 +21104,27 @@
       </c>
       <c r="D119" s="24" t="inlineStr">
         <is>
-          <t>목표 에너지 효율</t>
+          <t>산출 시각·대상 기간·모델</t>
         </is>
       </c>
       <c r="E119" s="24" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F119" s="24" t="inlineStr">
         <is>
-          <t>kWh/m³</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G119" s="24" t="inlineStr">
         <is>
-          <t>[파생: 현재 × (1 − 10%)]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H119" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.27·64]</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="I119" s="8" t="inlineStr">
@@ -21146,7 +21142,7 @@
     <row r="120" s="35">
       <c r="A120" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-017</t>
+          <t>REQ-AD-015</t>
         </is>
       </c>
       <c r="B120" s="24" t="inlineStr">
@@ -21161,17 +21157,17 @@
       </c>
       <c r="D120" s="24" t="inlineStr">
         <is>
-          <t>에너지 절감률</t>
+          <t>통신 상태</t>
         </is>
       </c>
       <c r="E120" s="24" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F120" s="24" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G120" s="24" t="inlineStr">
@@ -21181,12 +21177,12 @@
       </c>
       <c r="H120" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.27·64] ≥10%</t>
+          <t>[설계] 두절이면 권장값이 아예 없다 — 판별 유니온으로 두 상태를 분리</t>
         </is>
       </c>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr">
@@ -21199,32 +21195,32 @@
     <row r="121" s="35">
       <c r="A121" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-005</t>
+          <t>REQ-AD-015</t>
         </is>
       </c>
       <c r="B121" s="24" t="inlineStr">
         <is>
-          <t>SCR-OP-006</t>
+          <t>SCR-AD-001</t>
         </is>
       </c>
       <c r="C121" s="24" t="inlineStr">
         <is>
-          <t>운영 최적화</t>
+          <t>비용 절감 파생값</t>
         </is>
       </c>
       <c r="D121" s="24" t="inlineStr">
         <is>
-          <t>산출 시각·대상 기간·모델</t>
+          <t>약품비 절감률</t>
         </is>
       </c>
       <c r="E121" s="24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="F121" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G121" s="24" t="inlineStr">
@@ -21234,7 +21230,7 @@
       </c>
       <c r="H121" s="24" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>[원문 p.27·31] 검증 수준 20~30%</t>
         </is>
       </c>
       <c r="I121" s="8" t="inlineStr">
@@ -21252,32 +21248,32 @@
     <row r="122" s="35">
       <c r="A122" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-015</t>
+          <t>REQ-AD-017</t>
         </is>
       </c>
       <c r="B122" s="24" t="inlineStr">
         <is>
-          <t>SCR-OP-006</t>
+          <t>SCR-AD-001</t>
         </is>
       </c>
       <c r="C122" s="24" t="inlineStr">
         <is>
-          <t>운영 최적화</t>
+          <t>비용 절감 파생값</t>
         </is>
       </c>
       <c r="D122" s="24" t="inlineStr">
         <is>
-          <t>통신 상태</t>
+          <t>전력비 절감률</t>
         </is>
       </c>
       <c r="E122" s="24" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="F122" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G122" s="24" t="inlineStr">
@@ -21287,12 +21283,12 @@
       </c>
       <c r="H122" s="24" t="inlineStr">
         <is>
-          <t>[설계] 두절이면 권장값이 아예 없다 — 판별 유니온으로 두 상태를 분리</t>
+          <t>[원문 p.27·64] 목표 ≥10% — fixture는 목표값을 적용한다</t>
         </is>
       </c>
       <c r="I122" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J122" s="8" t="inlineStr">
@@ -21305,7 +21301,7 @@
     <row r="123" s="35">
       <c r="A123" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-015</t>
+          <t>REQ-AD-015·017</t>
         </is>
       </c>
       <c r="B123" s="24" t="inlineStr">
@@ -21320,7 +21316,7 @@
       </c>
       <c r="D123" s="24" t="inlineStr">
         <is>
-          <t>약품비 절감률</t>
+          <t>총 운영비 절감률</t>
         </is>
       </c>
       <c r="E123" s="24" t="inlineStr">
@@ -21335,12 +21331,12 @@
       </c>
       <c r="G123" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[파생: (약품 절감액 + 전력 절감액) ÷ (연 약품비 + 연 전력비)] 금액 가중이지 두 비율의 평균이 아니다</t>
         </is>
       </c>
       <c r="H123" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.27·31] 검증 수준 20~30%</t>
+          <t>[원문 p.27·31·64] 목표 ≥12%</t>
         </is>
       </c>
       <c r="I123" s="8" t="inlineStr">
@@ -21358,7 +21354,7 @@
     <row r="124" s="35">
       <c r="A124" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-017</t>
+          <t>REQ-AD-015</t>
         </is>
       </c>
       <c r="B124" s="24" t="inlineStr">
@@ -21373,7 +21369,7 @@
       </c>
       <c r="D124" s="24" t="inlineStr">
         <is>
-          <t>전력비 절감률</t>
+          <t>약품비 연 절감액</t>
         </is>
       </c>
       <c r="E124" s="24" t="inlineStr">
@@ -21383,17 +21379,17 @@
       </c>
       <c r="F124" s="24" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>원</t>
         </is>
       </c>
       <c r="G124" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[파생: 연 약품비 × 절감률]</t>
         </is>
       </c>
       <c r="H124" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.27·64] 목표 ≥10% — fixture는 목표값을 적용한다</t>
+          <t>기준액 [원문 p.34·40] 연 1,000만 원</t>
         </is>
       </c>
       <c r="I124" s="8" t="inlineStr">
@@ -21411,7 +21407,7 @@
     <row r="125" s="35">
       <c r="A125" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-015·017</t>
+          <t>REQ-AD-017</t>
         </is>
       </c>
       <c r="B125" s="24" t="inlineStr">
@@ -21426,7 +21422,7 @@
       </c>
       <c r="D125" s="24" t="inlineStr">
         <is>
-          <t>총 운영비 절감률</t>
+          <t>전력비 연 절감액</t>
         </is>
       </c>
       <c r="E125" s="24" t="inlineStr">
@@ -21436,17 +21432,17 @@
       </c>
       <c r="F125" s="24" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>원</t>
         </is>
       </c>
       <c r="G125" s="24" t="inlineStr">
         <is>
-          <t>[파생: (약품 절감액 + 전력 절감액) ÷ (연 약품비 + 연 전력비)] 금액 가중이지 두 비율의 평균이 아니다</t>
+          <t>[파생: 연 전력비 × 절감률]</t>
         </is>
       </c>
       <c r="H125" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.27·31·64] 목표 ≥12%</t>
+          <t>기준액 [원문 p.34·40] 연 500만 원</t>
         </is>
       </c>
       <c r="I125" s="8" t="inlineStr">
@@ -21464,7 +21460,7 @@
     <row r="126" s="35">
       <c r="A126" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-015</t>
+          <t>REQ-AD-015·017</t>
         </is>
       </c>
       <c r="B126" s="24" t="inlineStr">
@@ -21479,7 +21475,7 @@
       </c>
       <c r="D126" s="24" t="inlineStr">
         <is>
-          <t>약품비 연 절감액</t>
+          <t>연 절감액</t>
         </is>
       </c>
       <c r="E126" s="24" t="inlineStr">
@@ -21494,12 +21490,12 @@
       </c>
       <c r="G126" s="24" t="inlineStr">
         <is>
-          <t>[파생: 연 약품비 × 절감률]</t>
+          <t>[파생: 약품 + 전력] 사고 회피를 넣지 않는다</t>
         </is>
       </c>
       <c r="H126" s="24" t="inlineStr">
         <is>
-          <t>기준액 [원문 p.34·40] 연 1,000만 원</t>
+          <t>[설계: 실측 기반과 가정 기반을 합치지 않는다]</t>
         </is>
       </c>
       <c r="I126" s="8" t="inlineStr">
@@ -21517,7 +21513,7 @@
     <row r="127" s="35">
       <c r="A127" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-017</t>
+          <t>REQ-AD-015·017</t>
         </is>
       </c>
       <c r="B127" s="24" t="inlineStr">
@@ -21532,7 +21528,7 @@
       </c>
       <c r="D127" s="24" t="inlineStr">
         <is>
-          <t>전력비 연 절감액</t>
+          <t>월 절감액</t>
         </is>
       </c>
       <c r="E127" s="24" t="inlineStr">
@@ -21547,12 +21543,12 @@
       </c>
       <c r="G127" s="24" t="inlineStr">
         <is>
-          <t>[파생: 연 전력비 × 절감률]</t>
+          <t>[파생: 연 절감액 ÷ 12]</t>
         </is>
       </c>
       <c r="H127" s="24" t="inlineStr">
         <is>
-          <t>기준액 [원문 p.34·40] 연 500만 원</t>
+          <t>[설계]</t>
         </is>
       </c>
       <c r="I127" s="8" t="inlineStr">
@@ -21570,7 +21566,7 @@
     <row r="128" s="35">
       <c r="A128" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-015·017</t>
+          <t>REQ-AD-012</t>
         </is>
       </c>
       <c r="B128" s="24" t="inlineStr">
@@ -21585,7 +21581,7 @@
       </c>
       <c r="D128" s="24" t="inlineStr">
         <is>
-          <t>연 절감액</t>
+          <t>조기 탐지 건수</t>
         </is>
       </c>
       <c r="E128" s="24" t="inlineStr">
@@ -21595,17 +21591,17 @@
       </c>
       <c r="F128" s="24" t="inlineStr">
         <is>
-          <t>원</t>
+          <t>건</t>
         </is>
       </c>
       <c r="G128" s="24" t="inlineStr">
         <is>
-          <t>[파생: 약품 + 전력] 사고 회피를 넣지 않는다</t>
+          <t>[파생: 사업장의 이상 탐지 알람 수. 확인·조치 상태를 가리지 않는다]</t>
         </is>
       </c>
       <c r="H128" s="24" t="inlineStr">
         <is>
-          <t>[설계: 실측 기반과 가정 기반을 합치지 않는다]</t>
+          <t>[설계]</t>
         </is>
       </c>
       <c r="I128" s="8" t="inlineStr">
@@ -21623,7 +21619,7 @@
     <row r="129" s="35">
       <c r="A129" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-015·017</t>
+          <t>REQ-AD-012</t>
         </is>
       </c>
       <c r="B129" s="24" t="inlineStr">
@@ -21638,12 +21634,12 @@
       </c>
       <c r="D129" s="24" t="inlineStr">
         <is>
-          <t>월 절감액</t>
+          <t>회피 가능 비용</t>
         </is>
       </c>
       <c r="E129" s="24" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>[number, number]</t>
         </is>
       </c>
       <c r="F129" s="24" t="inlineStr">
@@ -21653,12 +21649,12 @@
       </c>
       <c r="G129" s="24" t="inlineStr">
         <is>
-          <t>[파생: 연 절감액 ÷ 12]</t>
+          <t>[파생: 건수 × 1,500만] ~ [파생: 건수 × 2,500만]</t>
         </is>
       </c>
       <c r="H129" s="24" t="inlineStr">
         <is>
-          <t>[설계]</t>
+          <t>[INC-93] 원문이 두 값을 준다(p.34·p.40). 하나를 고르지 않는다</t>
         </is>
       </c>
       <c r="I129" s="8" t="inlineStr">
@@ -21671,12 +21667,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K129" s="8" t="inlineStr"/>
+      <c r="K129" s="8" t="inlineStr">
+        <is>
+          <t>INC-93 원문 모순 — 채택안은 출처 열에 적었다</t>
+        </is>
+      </c>
     </row>
     <row r="130" s="35">
       <c r="A130" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-012</t>
+          <t>—</t>
         </is>
       </c>
       <c r="B130" s="24" t="inlineStr">
@@ -21691,27 +21691,27 @@
       </c>
       <c r="D130" s="24" t="inlineStr">
         <is>
-          <t>조기 탐지 건수</t>
+          <t>TMS 구축 비용 회피</t>
         </is>
       </c>
       <c r="E130" s="24" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>[number, number]</t>
         </is>
       </c>
       <c r="F130" s="24" t="inlineStr">
         <is>
-          <t>건</t>
+          <t>원</t>
         </is>
       </c>
       <c r="G130" s="24" t="inlineStr">
         <is>
-          <t>[파생: 사업장의 이상 탐지 알람 수. 확인·조치 상태를 가리지 않는다]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H130" s="24" t="inlineStr">
         <is>
-          <t>[설계]</t>
+          <t>[원문 p.40] 1.5억~2.5억(초년도) · 구축비 값 병존 [INC-36]</t>
         </is>
       </c>
       <c r="I130" s="8" t="inlineStr">
@@ -21724,12 +21724,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K130" s="8" t="inlineStr"/>
+      <c r="K130" s="8" t="inlineStr">
+        <is>
+          <t>INC-36 원문 모순 — 채택안은 출처 열에 적었다</t>
+        </is>
+      </c>
     </row>
     <row r="131" s="35">
       <c r="A131" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-012</t>
+          <t>—</t>
         </is>
       </c>
       <c r="B131" s="24" t="inlineStr">
@@ -21744,7 +21748,7 @@
       </c>
       <c r="D131" s="24" t="inlineStr">
         <is>
-          <t>회피 가능 비용</t>
+          <t>원문 연 절감 합계</t>
         </is>
       </c>
       <c r="E131" s="24" t="inlineStr">
@@ -21759,12 +21763,12 @@
       </c>
       <c r="G131" s="24" t="inlineStr">
         <is>
-          <t>[파생: 건수 × 1,500만] ~ [파생: 건수 × 2,500만]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H131" s="24" t="inlineStr">
         <is>
-          <t>[INC-93] 원문이 두 값을 준다(p.34·p.40). 하나를 고르지 않는다</t>
+          <t>[원문 p.40] 2,750~3,350만 · 항목 합계와 상한이 다르다 [INC-70]</t>
         </is>
       </c>
       <c r="I131" s="8" t="inlineStr">
@@ -21779,49 +21783,49 @@
       </c>
       <c r="K131" s="8" t="inlineStr">
         <is>
-          <t>INC-93 원문 모순 — 채택안은 출처 열에 적었다</t>
+          <t>INC-70 원문 모순 — 채택안은 출처 열에 적었다</t>
         </is>
       </c>
     </row>
     <row r="132" s="35">
       <c r="A132" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>REQ-AD-029</t>
         </is>
       </c>
       <c r="B132" s="24" t="inlineStr">
         <is>
-          <t>SCR-AD-001</t>
+          <t>SCR-OP-008</t>
         </is>
       </c>
       <c r="C132" s="24" t="inlineStr">
         <is>
-          <t>비용 절감 파생값</t>
+          <t>리포트 집계</t>
         </is>
       </c>
       <c r="D132" s="24" t="inlineStr">
         <is>
-          <t>TMS 구축 비용 회피</t>
+          <t>최신 이상 점수</t>
         </is>
       </c>
       <c r="E132" s="24" t="inlineStr">
         <is>
-          <t>[number, number]</t>
+          <t>number | null</t>
         </is>
       </c>
       <c r="F132" s="24" t="inlineStr">
         <is>
-          <t>원</t>
+          <t>점</t>
         </is>
       </c>
       <c r="G132" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[파생: 선택 기간 계열의 마지막 값]</t>
         </is>
       </c>
       <c r="H132" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.40] 1.5억~2.5억(초년도) · 구축비 값 병존 [INC-36]</t>
+          <t>[파생] 원본은 이상 점수 표의 값</t>
         </is>
       </c>
       <c r="I132" s="8" t="inlineStr">
@@ -21831,54 +21835,50 @@
       </c>
       <c r="J132" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K132" s="8" t="inlineStr">
-        <is>
-          <t>INC-36 원문 모순 — 채택안은 출처 열에 적었다</t>
-        </is>
-      </c>
+          <t>리포트 집계표 최신</t>
+        </is>
+      </c>
+      <c r="K132" s="8" t="inlineStr"/>
     </row>
     <row r="133" s="35">
       <c r="A133" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>REQ-AD-029</t>
         </is>
       </c>
       <c r="B133" s="24" t="inlineStr">
         <is>
-          <t>SCR-AD-001</t>
+          <t>SCR-OP-008</t>
         </is>
       </c>
       <c r="C133" s="24" t="inlineStr">
         <is>
-          <t>비용 절감 파생값</t>
+          <t>리포트 집계</t>
         </is>
       </c>
       <c r="D133" s="24" t="inlineStr">
         <is>
-          <t>원문 연 절감 합계</t>
+          <t>최대 이상 점수</t>
         </is>
       </c>
       <c r="E133" s="24" t="inlineStr">
         <is>
-          <t>[number, number]</t>
+          <t>number | null</t>
         </is>
       </c>
       <c r="F133" s="24" t="inlineStr">
         <is>
-          <t>원</t>
+          <t>점</t>
         </is>
       </c>
       <c r="G133" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[파생: 결측 제외 max]</t>
         </is>
       </c>
       <c r="H133" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.40] 2,750~3,350만 · 항목 합계와 상한이 다르다 [INC-70]</t>
+          <t>[파생] 원본은 이상 점수 표의 값</t>
         </is>
       </c>
       <c r="I133" s="8" t="inlineStr">
@@ -21888,14 +21888,10 @@
       </c>
       <c r="J133" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K133" s="8" t="inlineStr">
-        <is>
-          <t>INC-70 원문 모순 — 채택안은 출처 열에 적었다</t>
-        </is>
-      </c>
+          <t>리포트 집계표 최대</t>
+        </is>
+      </c>
+      <c r="K133" s="8" t="inlineStr"/>
     </row>
     <row r="134" s="35">
       <c r="A134" s="24" t="inlineStr">
@@ -21915,7 +21911,7 @@
       </c>
       <c r="D134" s="24" t="inlineStr">
         <is>
-          <t>최신 이상 점수</t>
+          <t>평균 이상 점수</t>
         </is>
       </c>
       <c r="E134" s="24" t="inlineStr">
@@ -21930,12 +21926,12 @@
       </c>
       <c r="G134" s="24" t="inlineStr">
         <is>
-          <t>[파생: 선택 기간 계열의 마지막 값]</t>
+          <t>[파생: 결측 제외 평균] · 표시 자릿수 1 [PROVISIONAL]</t>
         </is>
       </c>
       <c r="H134" s="24" t="inlineStr">
         <is>
-          <t>[파생] 원본은 이상 점수 표의 값</t>
+          <t>[파생] 원본은 이상 점수 표의 값 · E4 결측 제외</t>
         </is>
       </c>
       <c r="I134" s="8" t="inlineStr">
@@ -21945,10 +21941,14 @@
       </c>
       <c r="J134" s="8" t="inlineStr">
         <is>
-          <t>리포트 집계표 최신</t>
-        </is>
-      </c>
-      <c r="K134" s="8" t="inlineStr"/>
+          <t>리포트 집계표 평균</t>
+        </is>
+      </c>
+      <c r="K134" s="8" t="inlineStr">
+        <is>
+          <t>임시값 — 확정 시 src/shared/config/provisional.ts 한 파일을 교체한다</t>
+        </is>
+      </c>
     </row>
     <row r="135" s="35">
       <c r="A135" s="24" t="inlineStr">
@@ -21968,27 +21968,27 @@
       </c>
       <c r="D135" s="24" t="inlineStr">
         <is>
-          <t>최대 이상 점수</t>
+          <t>결측 표본 수</t>
         </is>
       </c>
       <c r="E135" s="24" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>number</t>
         </is>
       </c>
       <c r="F135" s="24" t="inlineStr">
         <is>
-          <t>점</t>
+          <t>건</t>
         </is>
       </c>
       <c r="G135" s="24" t="inlineStr">
         <is>
-          <t>[파생: 결측 제외 max]</t>
+          <t>[파생: null 개수]</t>
         </is>
       </c>
       <c r="H135" s="24" t="inlineStr">
         <is>
-          <t>[파생] 원본은 이상 점수 표의 값</t>
+          <t>[파생] E4 — 0으로 채우지 않는다</t>
         </is>
       </c>
       <c r="I135" s="8" t="inlineStr">
@@ -21998,7 +21998,7 @@
       </c>
       <c r="J135" s="8" t="inlineStr">
         <is>
-          <t>리포트 집계표 최대</t>
+          <t>요약표·집계표 결측</t>
         </is>
       </c>
       <c r="K135" s="8" t="inlineStr"/>
@@ -22021,27 +22021,27 @@
       </c>
       <c r="D136" s="24" t="inlineStr">
         <is>
-          <t>평균 이상 점수</t>
+          <t>전체 표본 수</t>
         </is>
       </c>
       <c r="E136" s="24" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>number</t>
         </is>
       </c>
       <c r="F136" s="24" t="inlineStr">
         <is>
-          <t>점</t>
+          <t>건</t>
         </is>
       </c>
       <c r="G136" s="24" t="inlineStr">
         <is>
-          <t>[파생: 결측 제외 평균] · 표시 자릿수 1 [PROVISIONAL]</t>
+          <t>[파생: 구간 표본 수]</t>
         </is>
       </c>
       <c r="H136" s="24" t="inlineStr">
         <is>
-          <t>[파생] 원본은 이상 점수 표의 값 · E4 결측 제외</t>
+          <t>[파생] 구간 길이 ÷ 수집 주기</t>
         </is>
       </c>
       <c r="I136" s="8" t="inlineStr">
@@ -22051,14 +22051,10 @@
       </c>
       <c r="J136" s="8" t="inlineStr">
         <is>
-          <t>리포트 집계표 평균</t>
-        </is>
-      </c>
-      <c r="K136" s="8" t="inlineStr">
-        <is>
-          <t>임시값 — 확정 시 src/shared/config/provisional.ts 한 파일을 교체한다</t>
-        </is>
-      </c>
+          <t>요약표·집계표 결측 분모</t>
+        </is>
+      </c>
+      <c r="K136" s="8" t="inlineStr"/>
     </row>
     <row r="137" s="35">
       <c r="A137" s="24" t="inlineStr">
@@ -22078,7 +22074,7 @@
       </c>
       <c r="D137" s="24" t="inlineStr">
         <is>
-          <t>결측 표본 수</t>
+          <t>알람 건수(우선순위별)</t>
         </is>
       </c>
       <c r="E137" s="24" t="inlineStr">
@@ -22093,12 +22089,12 @@
       </c>
       <c r="G137" s="24" t="inlineStr">
         <is>
-          <t>[파생: null 개수]</t>
+          <t>[파생: 사업장별 우선순위 집계]</t>
         </is>
       </c>
       <c r="H137" s="24" t="inlineStr">
         <is>
-          <t>[파생] E4 — 0으로 채우지 않는다</t>
+          <t>[파생] 원본은 알람 표의 값 · 우선순위 [원문 p.32]</t>
         </is>
       </c>
       <c r="I137" s="8" t="inlineStr">
@@ -22108,7 +22104,7 @@
       </c>
       <c r="J137" s="8" t="inlineStr">
         <is>
-          <t>요약표·집계표 결측</t>
+          <t>리포트 집계표 알람 3열</t>
         </is>
       </c>
       <c r="K137" s="8" t="inlineStr"/>
@@ -22116,42 +22112,42 @@
     <row r="138" s="35">
       <c r="A138" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-029</t>
+          <t>REQ-CO-012</t>
         </is>
       </c>
       <c r="B138" s="24" t="inlineStr">
         <is>
-          <t>SCR-OP-008</t>
+          <t>SCR-CO-001</t>
         </is>
       </c>
       <c r="C138" s="24" t="inlineStr">
         <is>
-          <t>리포트 집계</t>
+          <t>사용자·역할</t>
         </is>
       </c>
       <c r="D138" s="24" t="inlineStr">
         <is>
-          <t>전체 표본 수</t>
+          <t>역할</t>
         </is>
       </c>
       <c r="E138" s="24" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>site|gov|system</t>
         </is>
       </c>
       <c r="F138" s="24" t="inlineStr">
         <is>
-          <t>건</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G138" s="24" t="inlineStr">
         <is>
-          <t>[파생: 구간 표본 수]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H138" s="24" t="inlineStr">
         <is>
-          <t>[파생] 구간 길이 ÷ 수집 주기</t>
+          <t>[회의 2026-08-20] 사업장·기초지자체·시스템 관리자 — 원문 p.69의 관리자/운영자/게스트를 대체했다(회의가 원문을 이긴다, 설계 명세 색인)</t>
         </is>
       </c>
       <c r="I138" s="8" t="inlineStr">
@@ -22161,7 +22157,7 @@
       </c>
       <c r="J138" s="8" t="inlineStr">
         <is>
-          <t>요약표·집계표 결측 분모</t>
+          <t>헤더 프로필 메뉴</t>
         </is>
       </c>
       <c r="K138" s="8" t="inlineStr"/>
@@ -22169,42 +22165,42 @@
     <row r="139" s="35">
       <c r="A139" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-029</t>
+          <t>REQ-CO-012</t>
         </is>
       </c>
       <c r="B139" s="24" t="inlineStr">
         <is>
-          <t>SCR-OP-008</t>
+          <t>SCR-CO-001</t>
         </is>
       </c>
       <c r="C139" s="24" t="inlineStr">
         <is>
-          <t>리포트 집계</t>
+          <t>사용자·역할</t>
         </is>
       </c>
       <c r="D139" s="24" t="inlineStr">
         <is>
-          <t>알람 건수(우선순위별)</t>
+          <t>역할 라벨</t>
         </is>
       </c>
       <c r="E139" s="24" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F139" s="24" t="inlineStr">
         <is>
-          <t>건</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G139" s="24" t="inlineStr">
         <is>
-          <t>[파생: 사업장별 우선순위 집계]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H139" s="24" t="inlineStr">
         <is>
-          <t>[파생] 원본은 알람 표의 값 · 우선순위 [원문 p.32]</t>
+          <t>[회의 2026-08-20] 시스템 관리자 · 사업장 · 기초지자체 (개명 [사용자 요청 2026-08-24])</t>
         </is>
       </c>
       <c r="I139" s="8" t="inlineStr">
@@ -22214,7 +22210,7 @@
       </c>
       <c r="J139" s="8" t="inlineStr">
         <is>
-          <t>리포트 집계표 알람 3열</t>
+          <t>역할 전환 버튼</t>
         </is>
       </c>
       <c r="K139" s="8" t="inlineStr"/>
@@ -22237,12 +22233,12 @@
       </c>
       <c r="D140" s="24" t="inlineStr">
         <is>
-          <t>역할</t>
+          <t>역할 주체</t>
         </is>
       </c>
       <c r="E140" s="24" t="inlineStr">
         <is>
-          <t>admin|operator|guest</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F140" s="24" t="inlineStr">
@@ -22257,7 +22253,7 @@
       </c>
       <c r="H140" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.69] 3역할이 전부다</t>
+          <t>[회의 2026-08-20] 사업장=사업주·현장 담당자 · 기초지자체=기초자치단체 공무원 / 시스템 관리자=전체 총괄</t>
         </is>
       </c>
       <c r="I140" s="8" t="inlineStr">
@@ -22267,7 +22263,7 @@
       </c>
       <c r="J140" s="8" t="inlineStr">
         <is>
-          <t>헤더 프로필 메뉴</t>
+          <t>역할 전환 설명</t>
         </is>
       </c>
       <c r="K140" s="8" t="inlineStr"/>
@@ -22290,12 +22286,12 @@
       </c>
       <c r="D141" s="24" t="inlineStr">
         <is>
-          <t>역할 라벨</t>
+          <t>범위</t>
         </is>
       </c>
       <c r="E141" s="24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>all-sites|own-municipality|own-site</t>
         </is>
       </c>
       <c r="F141" s="24" t="inlineStr">
@@ -22310,20 +22306,24 @@
       </c>
       <c r="H141" s="24" t="inlineStr">
         <is>
-          <t>[원문 p.69] 관리자·운영자·게스트</t>
+          <t>[회의 2026-08-20] 원문에 없다 [TBD-08] · own-municipality는 타입에만 있고 필터가 없다(기초지자체 구현 보류 [사용자 지시 2026-08-20])</t>
         </is>
       </c>
       <c r="I141" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J141" s="8" t="inlineStr">
         <is>
-          <t>역할 전환 버튼</t>
-        </is>
-      </c>
-      <c r="K141" s="8" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K141" s="8" t="inlineStr">
+        <is>
+          <t>TBD-08 원문 미확정</t>
+        </is>
+      </c>
     </row>
     <row r="142" s="35">
       <c r="A142" s="24" t="inlineStr">
@@ -22343,7 +22343,7 @@
       </c>
       <c r="D142" s="24" t="inlineStr">
         <is>
-          <t>역할 주체</t>
+          <t>범위 라벨</t>
         </is>
       </c>
       <c r="E142" s="24" t="inlineStr">
@@ -22363,7 +22363,7 @@
       </c>
       <c r="H142" s="24" t="inlineStr">
         <is>
-          <t>[회의 2026-08-13] 관리자=사업주·최고 책임자 · 운영자=통합 관제 주체 / 게스트=[TBD-07] 추측</t>
+          <t>[회의 2026-08-20] 전 사업장 / 관할 시·군·구 / 자사 1개소</t>
         </is>
       </c>
       <c r="I142" s="8" t="inlineStr">
@@ -22376,11 +22376,7 @@
           <t>역할 전환 설명</t>
         </is>
       </c>
-      <c r="K142" s="8" t="inlineStr">
-        <is>
-          <t>TBD-07 원문 미확정</t>
-        </is>
-      </c>
+      <c r="K142" s="8" t="inlineStr"/>
     </row>
     <row r="143" s="35">
       <c r="A143" s="24" t="inlineStr">
@@ -22390,22 +22386,22 @@
       </c>
       <c r="B143" s="24" t="inlineStr">
         <is>
-          <t>SCR-CO-001</t>
+          <t>전 화면</t>
         </is>
       </c>
       <c r="C143" s="24" t="inlineStr">
         <is>
-          <t>사용자·역할</t>
+          <t>사업장 계정</t>
         </is>
       </c>
       <c r="D143" s="24" t="inlineStr">
         <is>
-          <t>범위</t>
+          <t>계정 키</t>
         </is>
       </c>
       <c r="E143" s="24" t="inlineStr">
         <is>
-          <t>all-sites|own-site</t>
+          <t>admin-1|admin-2</t>
         </is>
       </c>
       <c r="F143" s="24" t="inlineStr">
@@ -22420,7 +22416,7 @@
       </c>
       <c r="H143" s="24" t="inlineStr">
         <is>
-          <t>[회의 2026-08-13] 원문에 없다 [TBD-08]</t>
+          <t>[설계: 계정↔사업장 매핑이 원문에 없다(TBD-08). 범위 규칙 자체는 회의가 정했으므로 매핑만 시연값으로 채운다]</t>
         </is>
       </c>
       <c r="I143" s="8" t="inlineStr">
@@ -22447,17 +22443,17 @@
       </c>
       <c r="B144" s="24" t="inlineStr">
         <is>
-          <t>SCR-CO-001</t>
+          <t>전 화면</t>
         </is>
       </c>
       <c r="C144" s="24" t="inlineStr">
         <is>
-          <t>사용자·역할</t>
+          <t>사업장 계정</t>
         </is>
       </c>
       <c r="D144" s="24" t="inlineStr">
         <is>
-          <t>범위 라벨</t>
+          <t>계정 라벨</t>
         </is>
       </c>
       <c r="E144" s="24" t="inlineStr">
@@ -22477,7 +22473,7 @@
       </c>
       <c r="H144" s="24" t="inlineStr">
         <is>
-          <t>[회의 2026-08-13] 전 사업장 / 자사 1개소</t>
+          <t>[설계] 사업장1 · 사업장2</t>
         </is>
       </c>
       <c r="I144" s="8" t="inlineStr">
@@ -22487,7 +22483,7 @@
       </c>
       <c r="J144" s="8" t="inlineStr">
         <is>
-          <t>역할 전환 설명</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K144" s="8" t="inlineStr"/>
@@ -22505,17 +22501,17 @@
       </c>
       <c r="C145" s="24" t="inlineStr">
         <is>
-          <t>관리자 계정</t>
+          <t>사업장 계정</t>
         </is>
       </c>
       <c r="D145" s="24" t="inlineStr">
         <is>
-          <t>계정 키</t>
+          <t>소속 사업장</t>
         </is>
       </c>
       <c r="E145" s="24" t="inlineStr">
         <is>
-          <t>admin-1|admin-2</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F145" s="24" t="inlineStr">
@@ -22530,12 +22526,12 @@
       </c>
       <c r="H145" s="24" t="inlineStr">
         <is>
-          <t>[설계: 계정↔사업장 매핑이 원문에 없다(TBD-08). 범위 규칙 자체는 회의가 정했으므로 매핑만 시연값으로 채운다]</t>
+          <t>[TBD-08] 사업장 단위 데이터 접근 범위 · 시연값은 상태 대비로 골랐다</t>
         </is>
       </c>
       <c r="I145" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J145" s="8" t="inlineStr">
@@ -22552,22 +22548,22 @@
     <row r="146" s="35">
       <c r="A146" s="24" t="inlineStr">
         <is>
-          <t>REQ-CO-012</t>
+          <t>—</t>
         </is>
       </c>
       <c r="B146" s="24" t="inlineStr">
         <is>
-          <t>전 화면</t>
+          <t>SCR-AD-002</t>
         </is>
       </c>
       <c r="C146" s="24" t="inlineStr">
         <is>
-          <t>관리자 계정</t>
+          <t>공정</t>
         </is>
       </c>
       <c r="D146" s="24" t="inlineStr">
         <is>
-          <t>계정 라벨</t>
+          <t>단계 ID</t>
         </is>
       </c>
       <c r="E146" s="24" t="inlineStr">
@@ -22587,12 +22583,12 @@
       </c>
       <c r="H146" s="24" t="inlineStr">
         <is>
-          <t>[설계] 관리자1 · 관리자2</t>
+          <t>[설계] URL 쿼리 ?stage=에 실린다</t>
         </is>
       </c>
       <c r="I146" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J146" s="8" t="inlineStr">
@@ -22605,27 +22601,27 @@
     <row r="147" s="35">
       <c r="A147" s="24" t="inlineStr">
         <is>
-          <t>REQ-CO-012</t>
+          <t>—</t>
         </is>
       </c>
       <c r="B147" s="24" t="inlineStr">
         <is>
-          <t>전 화면</t>
+          <t>SCR-AD-002</t>
         </is>
       </c>
       <c r="C147" s="24" t="inlineStr">
         <is>
-          <t>관리자 계정</t>
+          <t>공정</t>
         </is>
       </c>
       <c r="D147" s="24" t="inlineStr">
         <is>
-          <t>소속 사업장</t>
+          <t>단계 순번·이름</t>
         </is>
       </c>
       <c r="E147" s="24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number · string</t>
         </is>
       </c>
       <c r="F147" s="24" t="inlineStr">
@@ -22640,7 +22636,7 @@
       </c>
       <c r="H147" s="24" t="inlineStr">
         <is>
-          <t>[TBD-08] 사업장 단위 데이터 접근 범위 · 시연값은 상태 대비로 골랐다</t>
+          <t>[설계] 표준 6단계 — 사용자 제공 자료</t>
         </is>
       </c>
       <c r="I147" s="8" t="inlineStr">
@@ -22653,11 +22649,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K147" s="8" t="inlineStr">
-        <is>
-          <t>TBD-08 원문 미확정</t>
-        </is>
-      </c>
+      <c r="K147" s="8" t="inlineStr"/>
     </row>
     <row r="148" s="35">
       <c r="A148" s="24" t="inlineStr">
@@ -22677,12 +22669,12 @@
       </c>
       <c r="D148" s="24" t="inlineStr">
         <is>
-          <t>단계 ID</t>
+          <t>처리 유형</t>
         </is>
       </c>
       <c r="E148" s="24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>physical|biological|chemical|monitoring</t>
         </is>
       </c>
       <c r="F148" s="24" t="inlineStr">
@@ -22697,12 +22689,12 @@
       </c>
       <c r="H148" s="24" t="inlineStr">
         <is>
-          <t>[설계] URL 쿼리 ?stage=에 실린다</t>
+          <t>[공정자료 p.6] 화학·생물 결합 구조</t>
         </is>
       </c>
       <c r="I148" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J148" s="8" t="inlineStr">
@@ -22730,12 +22722,12 @@
       </c>
       <c r="D149" s="24" t="inlineStr">
         <is>
-          <t>단계 순번·이름</t>
+          <t>하위 조(槽)</t>
         </is>
       </c>
       <c r="E149" s="24" t="inlineStr">
         <is>
-          <t>number · string</t>
+          <t>string[]</t>
         </is>
       </c>
       <c r="F149" s="24" t="inlineStr">
@@ -22750,7 +22742,7 @@
       </c>
       <c r="H149" s="24" t="inlineStr">
         <is>
-          <t>[설계] 표준 6단계 — 사용자 제공 자료</t>
+          <t>[공정자료 p.4] + [설계] 집수조·유량조정조</t>
         </is>
       </c>
       <c r="I149" s="8" t="inlineStr">
@@ -22783,12 +22775,12 @@
       </c>
       <c r="D150" s="24" t="inlineStr">
         <is>
-          <t>처리 유형</t>
+          <t>계측 등급</t>
         </is>
       </c>
       <c r="E150" s="24" t="inlineStr">
         <is>
-          <t>physical|biological|chemical|monitoring</t>
+          <t>actual|estimated|none</t>
         </is>
       </c>
       <c r="F150" s="24" t="inlineStr">
@@ -22803,7 +22795,7 @@
       </c>
       <c r="H150" s="24" t="inlineStr">
         <is>
-          <t>[공정자료 p.6] 화학·생물 결합 구조</t>
+          <t>[PROVISIONAL] 원문에 등급 개념 없음</t>
         </is>
       </c>
       <c r="I150" s="8" t="inlineStr">
@@ -22816,7 +22808,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K150" s="8" t="inlineStr"/>
+      <c r="K150" s="8" t="inlineStr">
+        <is>
+          <t>임시값 — 확정 시 src/shared/config/provisional.ts 한 파일을 교체한다</t>
+        </is>
+      </c>
     </row>
     <row r="151" s="35">
       <c r="A151" s="24" t="inlineStr">
@@ -22836,12 +22832,12 @@
       </c>
       <c r="D151" s="24" t="inlineStr">
         <is>
-          <t>하위 조(槽)</t>
+          <t>계측 설명</t>
         </is>
       </c>
       <c r="E151" s="24" t="inlineStr">
         <is>
-          <t>string[]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F151" s="24" t="inlineStr">
@@ -22856,7 +22852,7 @@
       </c>
       <c r="H151" s="24" t="inlineStr">
         <is>
-          <t>[공정자료 p.4] + [설계] 집수조·유량조정조</t>
+          <t>[설계] 계측이 없으면 왜 없는지를 적는다</t>
         </is>
       </c>
       <c r="I151" s="8" t="inlineStr">
@@ -22889,12 +22885,12 @@
       </c>
       <c r="D152" s="24" t="inlineStr">
         <is>
-          <t>계측 등급</t>
+          <t>배치 설비 ID</t>
         </is>
       </c>
       <c r="E152" s="24" t="inlineStr">
         <is>
-          <t>actual|estimated|none</t>
+          <t>string[]</t>
         </is>
       </c>
       <c r="F152" s="24" t="inlineStr">
@@ -22909,7 +22905,7 @@
       </c>
       <c r="H152" s="24" t="inlineStr">
         <is>
-          <t>[PROVISIONAL] 원문에 등급 개념 없음</t>
+          <t>[설계] 설비 4대 — 개수는 시연값</t>
         </is>
       </c>
       <c r="I152" s="8" t="inlineStr">
@@ -22922,16 +22918,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K152" s="8" t="inlineStr">
-        <is>
-          <t>임시값 — 확정 시 src/shared/config/provisional.ts 한 파일을 교체한다</t>
-        </is>
-      </c>
+      <c r="K152" s="8" t="inlineStr"/>
     </row>
     <row r="153" s="35">
       <c r="A153" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>REQ-AD-003</t>
         </is>
       </c>
       <c r="B153" s="24" t="inlineStr">
@@ -22946,12 +22938,12 @@
       </c>
       <c r="D153" s="24" t="inlineStr">
         <is>
-          <t>계측 설명</t>
+          <t>가동 여부</t>
         </is>
       </c>
       <c r="E153" s="24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F153" s="24" t="inlineStr">
@@ -22961,12 +22953,12 @@
       </c>
       <c r="G153" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[파생: 전류·전력 채널 시간별 0/1]</t>
         </is>
       </c>
       <c r="H153" s="24" t="inlineStr">
         <is>
-          <t>[설계] 계측이 없으면 왜 없는지를 적는다</t>
+          <t>[데이터셋 docs/datasets/Non_TMS_sites/04_사업장_유량,전력,전류 가동시간]</t>
         </is>
       </c>
       <c r="I153" s="8" t="inlineStr">
@@ -22984,7 +22976,7 @@
     <row r="154" s="35">
       <c r="A154" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>REQ-AD-003</t>
         </is>
       </c>
       <c r="B154" s="24" t="inlineStr">
@@ -22999,12 +22991,12 @@
       </c>
       <c r="D154" s="24" t="inlineStr">
         <is>
-          <t>배치 설비 ID</t>
+          <t>방류 여부</t>
         </is>
       </c>
       <c r="E154" s="24" t="inlineStr">
         <is>
-          <t>string[]</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F154" s="24" t="inlineStr">
@@ -23014,12 +23006,12 @@
       </c>
       <c r="G154" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[파생: 유량 채널 시간별 0/1]</t>
         </is>
       </c>
       <c r="H154" s="24" t="inlineStr">
         <is>
-          <t>[설계] 설비 4대 — 개수는 시연값</t>
+          <t>위와 같음 — 진유원 88.3%, 하루 3~24시간 변동</t>
         </is>
       </c>
       <c r="I154" s="8" t="inlineStr">
@@ -23037,7 +23029,7 @@
     <row r="155" s="35">
       <c r="A155" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-003</t>
+          <t>—</t>
         </is>
       </c>
       <c r="B155" s="24" t="inlineStr">
@@ -23052,12 +23044,12 @@
       </c>
       <c r="D155" s="24" t="inlineStr">
         <is>
-          <t>가동 여부</t>
+          <t>방류 중단 시간</t>
         </is>
       </c>
       <c r="E155" s="24" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number | null</t>
         </is>
       </c>
       <c r="F155" s="24" t="inlineStr">
@@ -23067,12 +23059,12 @@
       </c>
       <c r="G155" s="24" t="inlineStr">
         <is>
-          <t>[파생: 전류·전력 채널 시간별 0/1]</t>
+          <t>[파생: 유량 채널이 0인 연속 시간]</t>
         </is>
       </c>
       <c r="H155" s="24" t="inlineStr">
         <is>
-          <t>[데이터셋 docs/datasets/Non_TMS_sites/04_사업장_유량,전력,전류 가동시간]</t>
+          <t>위와 같음 · 방류 중이면 null</t>
         </is>
       </c>
       <c r="I155" s="8" t="inlineStr">
@@ -23090,7 +23082,7 @@
     <row r="156" s="35">
       <c r="A156" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-003</t>
+          <t>—</t>
         </is>
       </c>
       <c r="B156" s="24" t="inlineStr">
@@ -23105,12 +23097,12 @@
       </c>
       <c r="D156" s="24" t="inlineStr">
         <is>
-          <t>방류 여부</t>
+          <t>운영 분류</t>
         </is>
       </c>
       <c r="E156" s="24" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F156" s="24" t="inlineStr">
@@ -23120,12 +23112,12 @@
       </c>
       <c r="G156" s="24" t="inlineStr">
         <is>
-          <t>[파생: 유량 채널 시간별 0/1]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H156" s="24" t="inlineStr">
         <is>
-          <t>위와 같음 — 진유원 88.3%, 하루 3~24시간 변동</t>
+          <t>위와 같음 가동배출 = 상시가동 간헐방류</t>
         </is>
       </c>
       <c r="I156" s="8" t="inlineStr">
@@ -23143,12 +23135,12 @@
     <row r="157" s="35">
       <c r="A157" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>REQ-AD-003</t>
         </is>
       </c>
       <c r="B157" s="24" t="inlineStr">
         <is>
-          <t>SCR-AD-002</t>
+          <t>SCR-OP-008</t>
         </is>
       </c>
       <c r="C157" s="24" t="inlineStr">
@@ -23158,7 +23150,7 @@
       </c>
       <c r="D157" s="24" t="inlineStr">
         <is>
-          <t>방류 중단 시간</t>
+          <t>방류 시간</t>
         </is>
       </c>
       <c r="E157" s="24" t="inlineStr">
@@ -23173,12 +23165,12 @@
       </c>
       <c r="G157" s="24" t="inlineStr">
         <is>
-          <t>[파생: 유량 채널이 0인 연속 시간]</t>
+          <t>[파생: 방류 확인 표본 ÷ 시간당 표본]</t>
         </is>
       </c>
       <c r="H157" s="24" t="inlineStr">
         <is>
-          <t>위와 같음 · 방류 중이면 null</t>
+          <t>위와 같음 · null = 통신 두절로 모름</t>
         </is>
       </c>
       <c r="I157" s="8" t="inlineStr">
@@ -23196,12 +23188,12 @@
     <row r="158" s="35">
       <c r="A158" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>REQ-AD-024</t>
         </is>
       </c>
       <c r="B158" s="24" t="inlineStr">
         <is>
-          <t>SCR-AD-002</t>
+          <t>SCR-OP-007</t>
         </is>
       </c>
       <c r="C158" s="24" t="inlineStr">
@@ -23211,12 +23203,12 @@
       </c>
       <c r="D158" s="24" t="inlineStr">
         <is>
-          <t>운영 분류</t>
+          <t>비방류 중 발생</t>
         </is>
       </c>
       <c r="E158" s="24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F158" s="24" t="inlineStr">
@@ -23226,12 +23218,12 @@
       </c>
       <c r="G158" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[파생: 발생 시각 → 방류 여부]</t>
         </is>
       </c>
       <c r="H158" s="24" t="inlineStr">
         <is>
-          <t>위와 같음 가동배출 = 상시가동 간헐방류</t>
+          <t>위와 같음 · 수질 계열 알람 2종에만</t>
         </is>
       </c>
       <c r="I158" s="8" t="inlineStr">
@@ -23249,12 +23241,12 @@
     <row r="159" s="35">
       <c r="A159" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-003</t>
+          <t>REQ-AD-004</t>
         </is>
       </c>
       <c r="B159" s="24" t="inlineStr">
         <is>
-          <t>SCR-OP-008</t>
+          <t>SCR-AD-003</t>
         </is>
       </c>
       <c r="C159" s="24" t="inlineStr">
@@ -23264,12 +23256,12 @@
       </c>
       <c r="D159" s="24" t="inlineStr">
         <is>
-          <t>방류 시간</t>
+          <t>가동 여부(표본별)</t>
         </is>
       </c>
       <c r="E159" s="24" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>boolean | null</t>
         </is>
       </c>
       <c r="F159" s="24" t="inlineStr">
@@ -23279,12 +23271,12 @@
       </c>
       <c r="G159" s="24" t="inlineStr">
         <is>
-          <t>[파생: 방류 확인 표본 ÷ 시간당 표본]</t>
+          <t>[파생: current &gt; 0]</t>
         </is>
       </c>
       <c r="H159" s="24" t="inlineStr">
         <is>
-          <t>위와 같음 · null = 통신 두절로 모름</t>
+          <t>위와 같음 전류계위치 = 유입펌프</t>
         </is>
       </c>
       <c r="I159" s="8" t="inlineStr">
@@ -23302,12 +23294,12 @@
     <row r="160" s="35">
       <c r="A160" s="24" t="inlineStr">
         <is>
-          <t>REQ-AD-024</t>
+          <t>REQ-AD-004</t>
         </is>
       </c>
       <c r="B160" s="24" t="inlineStr">
         <is>
-          <t>SCR-OP-007</t>
+          <t>SCR-AD-003</t>
         </is>
       </c>
       <c r="C160" s="24" t="inlineStr">
@@ -23317,12 +23309,12 @@
       </c>
       <c r="D160" s="24" t="inlineStr">
         <is>
-          <t>비방류 중 발생</t>
+          <t>방류 여부(표본별)</t>
         </is>
       </c>
       <c r="E160" s="24" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>boolean | null</t>
         </is>
       </c>
       <c r="F160" s="24" t="inlineStr">
@@ -23332,12 +23324,12 @@
       </c>
       <c r="G160" s="24" t="inlineStr">
         <is>
-          <t>[파생: 발생 시각 → 방류 여부]</t>
+          <t>[파생: isDischargingAt]</t>
         </is>
       </c>
       <c r="H160" s="24" t="inlineStr">
         <is>
-          <t>위와 같음 · 수질 계열 알람 2종에만</t>
+          <t>위와 같음</t>
         </is>
       </c>
       <c r="I160" s="8" t="inlineStr">
@@ -23370,12 +23362,12 @@
       </c>
       <c r="D161" s="24" t="inlineStr">
         <is>
-          <t>가동 여부(표본별)</t>
+          <t>결측 여부(표본별)</t>
         </is>
       </c>
       <c r="E161" s="24" t="inlineStr">
         <is>
-          <t>boolean | null</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F161" s="24" t="inlineStr">
@@ -23385,12 +23377,12 @@
       </c>
       <c r="G161" s="24" t="inlineStr">
         <is>
-          <t>[파생: current &gt; 0]</t>
+          <t>[파생: isMissingAt]</t>
         </is>
       </c>
       <c r="H161" s="24" t="inlineStr">
         <is>
-          <t>위와 같음 전류계위치 = 유입펌프</t>
+          <t>[설계] 리본 수신 행</t>
         </is>
       </c>
       <c r="I161" s="8" t="inlineStr">
@@ -23406,109 +23398,29 @@
       <c r="K161" s="8" t="inlineStr"/>
     </row>
     <row r="162" s="35">
-      <c r="A162" s="24" t="inlineStr">
-        <is>
-          <t>REQ-AD-004</t>
-        </is>
-      </c>
-      <c r="B162" s="24" t="inlineStr">
-        <is>
-          <t>SCR-AD-003</t>
-        </is>
-      </c>
-      <c r="C162" s="24" t="inlineStr">
-        <is>
-          <t>공정</t>
-        </is>
-      </c>
-      <c r="D162" s="24" t="inlineStr">
-        <is>
-          <t>방류 여부(표본별)</t>
-        </is>
-      </c>
-      <c r="E162" s="24" t="inlineStr">
-        <is>
-          <t>boolean | null</t>
-        </is>
-      </c>
-      <c r="F162" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G162" s="24" t="inlineStr">
-        <is>
-          <t>[파생: isDischargingAt]</t>
-        </is>
-      </c>
-      <c r="H162" s="24" t="inlineStr">
-        <is>
-          <t>위와 같음</t>
-        </is>
-      </c>
-      <c r="I162" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J162" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="A162" s="24" t="n"/>
+      <c r="B162" s="24" t="n"/>
+      <c r="C162" s="24" t="n"/>
+      <c r="D162" s="24" t="n"/>
+      <c r="E162" s="24" t="n"/>
+      <c r="F162" s="24" t="n"/>
+      <c r="G162" s="24" t="n"/>
+      <c r="H162" s="24" t="n"/>
+      <c r="I162" s="8" t="n"/>
+      <c r="J162" s="8" t="n"/>
       <c r="K162" s="8" t="inlineStr"/>
     </row>
     <row r="163" s="35">
-      <c r="A163" s="24" t="inlineStr">
-        <is>
-          <t>REQ-AD-004</t>
-        </is>
-      </c>
-      <c r="B163" s="24" t="inlineStr">
-        <is>
-          <t>SCR-AD-003</t>
-        </is>
-      </c>
-      <c r="C163" s="24" t="inlineStr">
-        <is>
-          <t>공정</t>
-        </is>
-      </c>
-      <c r="D163" s="24" t="inlineStr">
-        <is>
-          <t>결측 여부(표본별)</t>
-        </is>
-      </c>
-      <c r="E163" s="24" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="F163" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G163" s="24" t="inlineStr">
-        <is>
-          <t>[파생: isMissingAt]</t>
-        </is>
-      </c>
-      <c r="H163" s="24" t="inlineStr">
-        <is>
-          <t>[설계] 리본 수신 행</t>
-        </is>
-      </c>
-      <c r="I163" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J163" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="A163" s="24" t="n"/>
+      <c r="B163" s="24" t="n"/>
+      <c r="C163" s="24" t="n"/>
+      <c r="D163" s="24" t="n"/>
+      <c r="E163" s="24" t="n"/>
+      <c r="F163" s="24" t="n"/>
+      <c r="G163" s="24" t="n"/>
+      <c r="H163" s="24" t="n"/>
+      <c r="I163" s="8" t="n"/>
+      <c r="J163" s="8" t="n"/>
       <c r="K163" s="8" t="inlineStr"/>
     </row>
     <row r="164" ht="15.75" customHeight="1" s="35"/>
